--- a/xlsx/HWV.xlsx
+++ b/xlsx/HWV.xlsx
@@ -2470,7 +2470,7 @@
     <t>Motet</t>
   </si>
   <si>
-    <t>motet pour soprano avec cordes (2 violons) et basse continue</t>
+    <t>soprano avec cordes (2 violons) et basse continue</t>
   </si>
   <si>
     <t>pour la fête de St. Antoine de Padoue
@@ -2569,7 +2569,7 @@
     <t>O qualis de coelo sonus</t>
   </si>
   <si>
-    <t>motet pour soprano solo avec cordes (2 violons) et basse continue</t>
+    <t>soprano solo avec cordes (2 violons) et basse continue</t>
   </si>
   <si>
     <t>HWV 240</t>
@@ -2578,7 +2578,7 @@
     <t>Saeviat tellus inter rigores</t>
   </si>
   <si>
-    <t>motet pour soprano solo avec orchestre (2 hautbois, 2 violons, alto) et basse continue</t>
+    <t>soprano solo avec orchestre (2 hautbois, 2 violons, alto) et basse continue</t>
   </si>
   <si>
     <t>pour la Madonne très sainte de Carmine
@@ -2603,7 +2603,7 @@
     <t>Silete venti</t>
   </si>
   <si>
-    <t>motet pour soprano solo avec orrchestre (2 hautbois, basson, 2 violons, alto, violoncelle) et basse continue</t>
+    <t>soprano solo avec orrchestre (2 hautbois, basson, 2 violons, alto, violoncelle) et basse continue</t>
   </si>
   <si>
     <t>HWV 243</t>
@@ -2624,7 +2624,7 @@
     <t>Kyrie eleison</t>
   </si>
   <si>
-    <t>pour 4 voix (SATB) avec cordes (2 violons, 2 altos) et basse continue</t>
+    <t>4 voix (SATB) avec cordes (2 violons, 2 altos) et basse continue</t>
   </si>
   <si>
     <t>HWV 245</t>
@@ -2633,7 +2633,7 @@
     <t>Gloria in excelsis Deo</t>
   </si>
   <si>
-    <t>pour 5-6 voix (SSATTB) avec orchestre (hautbois, trompette, 2 violons, 2 altos), orgue et basse continue</t>
+    <t>5-6 voix (SSATTB) avec orchestre (hautbois, trompette, 2 violons, 2 altos), orgue et basse continue</t>
   </si>
   <si>
     <t>HWV 269</t>
@@ -7490,13 +7490,10 @@
     <col min="4" max="4" width="26.7117117117117" style="1" customWidth="1"/>
     <col min="5" max="5" width="16.9099099099099" style="2" customWidth="1"/>
     <col min="6" max="6" width="13.5855855855856" style="2" customWidth="1"/>
-    <col min="7" max="7" width="22.1621621621622" style="1" customWidth="1"/>
+    <col min="7" max="7" width="42.9369369369369" style="1" customWidth="1"/>
     <col min="8" max="8" width="36.8378378378378" style="1" customWidth="1"/>
     <col min="9" max="9" width="48.8828828828829" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8.61261261261261" style="1"/>
-    <col min="11" max="11" width="19.4594594594595" style="1" customWidth="1"/>
-    <col min="12" max="16381" width="8.61261261261261" style="1"/>
-    <col min="16383" max="16384" width="8.61261261261261" style="1"/>
+    <col min="10" max="16384" width="8.61261261261261" style="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="16.7" spans="1:9">
@@ -21674,7 +21671,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="C1:E1 G1 I1" formula="1"/>
+    <ignoredError sqref="I1 G1 C1:E1" formula="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/xlsx/HWV.xlsx
+++ b/xlsx/HWV.xlsx
@@ -15,7 +15,7 @@
     <sheet name="HWV" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">HWV!$A$1:$J$656</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">HWV!$A$1:$J$669</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3397" uniqueCount="1769">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3425" uniqueCount="1789">
   <si>
     <t>SORT</t>
   </si>
@@ -5140,9 +5140,6 @@
     <t>HWV 444</t>
   </si>
   <si>
-    <t>Partita, en do mineur, pour clavecin</t>
-  </si>
-  <si>
     <t>Partita</t>
   </si>
   <si>
@@ -5225,9 +5222,6 @@
     <t>HWV 450</t>
   </si>
   <si>
-    <t>Partita, en sol majeur, pour clavecin</t>
-  </si>
-  <si>
     <t>1. Prélude (sol majeur)
 2. Allemande (sol majeur)
 3. Courante (sol majeur)
@@ -5267,9 +5261,6 @@
   </si>
   <si>
     <t>HWV 454</t>
-  </si>
-  <si>
-    <t>Partita, en la majeur, pour clavecin</t>
   </si>
   <si>
     <t>1. Allemande (la majeur)
@@ -6055,9 +6046,6 @@
     <t>HWV 578</t>
   </si>
   <si>
-    <t>Sonate, trio, gavotte</t>
-  </si>
-  <si>
     <t>1. Sonate. Allegro (so majeur)
 [voir HWV 277]
 2. Trio. Larghetto (do majeur)
@@ -6259,6 +6247,78 @@
   </si>
   <si>
     <t>HWV 612</t>
+  </si>
+  <si>
+    <t>HWV A1</t>
+  </si>
+  <si>
+    <t>L'Elpidia, overo Li rivali generosi</t>
+  </si>
+  <si>
+    <t>HWV A2</t>
+  </si>
+  <si>
+    <t>HWV A3</t>
+  </si>
+  <si>
+    <t>Ormisda</t>
+  </si>
+  <si>
+    <t>HWV A4</t>
+  </si>
+  <si>
+    <t>Venceslao</t>
+  </si>
+  <si>
+    <t>HWV A5</t>
+  </si>
+  <si>
+    <t>HWV A6</t>
+  </si>
+  <si>
+    <t>Lucio Papirio dittatore</t>
+  </si>
+  <si>
+    <t>HWV A7</t>
+  </si>
+  <si>
+    <t>Catone</t>
+  </si>
+  <si>
+    <t>HWV A8</t>
+  </si>
+  <si>
+    <t>Semiramide, or Semiramis riconosciuta</t>
+  </si>
+  <si>
+    <t>HWV A9</t>
+  </si>
+  <si>
+    <t>Caio Fabricio</t>
+  </si>
+  <si>
+    <t>HWV A10</t>
+  </si>
+  <si>
+    <t>Arbace</t>
+  </si>
+  <si>
+    <t>HWV A11</t>
+  </si>
+  <si>
+    <t>Didone</t>
+  </si>
+  <si>
+    <t>HWV A12</t>
+  </si>
+  <si>
+    <t>HWV A15</t>
+  </si>
+  <si>
+    <t>37 Minuets</t>
+  </si>
+  <si>
+    <t>Arranged from music of opera arias</t>
   </si>
 </sst>
 </file>
@@ -6917,7 +6977,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6959,15 +7019,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="58" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -7500,10 +7551,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J656"/>
+  <dimension ref="A1:J669"/>
   <sheetFormatPr defaultColWidth="8.61261261261261" defaultRowHeight="30" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="14.4414414414414" style="3" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="14.4414414414414" style="3" customWidth="1"/>
     <col min="2" max="4" width="14.4414414414414" style="1" customWidth="1"/>
     <col min="5" max="5" width="30.5765765765766" style="2" customWidth="1"/>
     <col min="6" max="7" width="11.6576576576577" style="1" customWidth="1"/>
@@ -13895,19 +13946,19 @@
       <c r="A263" s="6">
         <v>229</v>
       </c>
-      <c r="B263" s="14" t="s">
+      <c r="B263" s="7" t="s">
         <v>756</v>
       </c>
-      <c r="C263" s="15"/>
-      <c r="D263" s="15"/>
-      <c r="E263" s="15" t="s">
+      <c r="C263" s="9"/>
+      <c r="D263" s="9"/>
+      <c r="E263" s="9" t="s">
         <v>757</v>
       </c>
       <c r="F263" s="9"/>
       <c r="G263" s="9"/>
       <c r="H263" s="9"/>
       <c r="I263" s="9"/>
-      <c r="J263" s="16" t="s">
+      <c r="J263" s="11" t="s">
         <v>758</v>
       </c>
     </row>
@@ -13915,21 +13966,21 @@
       <c r="A264" s="6">
         <v>229.1</v>
       </c>
-      <c r="B264" s="14" t="s">
+      <c r="B264" s="7" t="s">
         <v>759</v>
       </c>
-      <c r="C264" s="15"/>
-      <c r="D264" s="15"/>
-      <c r="E264" s="15" t="s">
+      <c r="C264" s="9"/>
+      <c r="D264" s="9"/>
+      <c r="E264" s="9" t="s">
         <v>760</v>
       </c>
       <c r="F264" s="9"/>
       <c r="G264" s="9"/>
       <c r="H264" s="9"/>
-      <c r="I264" s="15" t="s">
+      <c r="I264" s="9" t="s">
         <v>761</v>
       </c>
-      <c r="J264" s="15" t="s">
+      <c r="J264" s="9" t="s">
         <v>762</v>
       </c>
     </row>
@@ -13937,21 +13988,21 @@
       <c r="A265" s="6">
         <v>229.2</v>
       </c>
-      <c r="B265" s="14" t="s">
+      <c r="B265" s="7" t="s">
         <v>763</v>
       </c>
-      <c r="C265" s="15"/>
-      <c r="D265" s="15"/>
-      <c r="E265" s="15" t="s">
+      <c r="C265" s="9"/>
+      <c r="D265" s="9"/>
+      <c r="E265" s="9" t="s">
         <v>764</v>
       </c>
       <c r="F265" s="9"/>
       <c r="G265" s="9"/>
       <c r="H265" s="9"/>
-      <c r="I265" s="15" t="s">
+      <c r="I265" s="9" t="s">
         <v>765</v>
       </c>
-      <c r="J265" s="15" t="s">
+      <c r="J265" s="9" t="s">
         <v>766</v>
       </c>
     </row>
@@ -13959,18 +14010,18 @@
       <c r="A266" s="6">
         <v>229.3</v>
       </c>
-      <c r="B266" s="14" t="s">
+      <c r="B266" s="7" t="s">
         <v>767</v>
       </c>
-      <c r="C266" s="15"/>
-      <c r="D266" s="15"/>
-      <c r="E266" s="15" t="s">
+      <c r="C266" s="9"/>
+      <c r="D266" s="9"/>
+      <c r="E266" s="9" t="s">
         <v>768</v>
       </c>
       <c r="F266" s="9"/>
       <c r="G266" s="9"/>
       <c r="H266" s="9"/>
-      <c r="I266" s="15" t="s">
+      <c r="I266" s="9" t="s">
         <v>769</v>
       </c>
       <c r="J266" s="9"/>
@@ -13979,21 +14030,21 @@
       <c r="A267" s="6">
         <v>229.4</v>
       </c>
-      <c r="B267" s="14" t="s">
+      <c r="B267" s="7" t="s">
         <v>770</v>
       </c>
-      <c r="C267" s="15"/>
-      <c r="D267" s="15"/>
-      <c r="E267" s="15" t="s">
+      <c r="C267" s="9"/>
+      <c r="D267" s="9"/>
+      <c r="E267" s="9" t="s">
         <v>771</v>
       </c>
       <c r="F267" s="9"/>
       <c r="G267" s="9"/>
       <c r="H267" s="9"/>
-      <c r="I267" s="15" t="s">
+      <c r="I267" s="9" t="s">
         <v>772</v>
       </c>
-      <c r="J267" s="15" t="s">
+      <c r="J267" s="9" t="s">
         <v>773</v>
       </c>
     </row>
@@ -14001,21 +14052,21 @@
       <c r="A268" s="6">
         <v>229.5</v>
       </c>
-      <c r="B268" s="14" t="s">
+      <c r="B268" s="7" t="s">
         <v>774</v>
       </c>
-      <c r="C268" s="15"/>
-      <c r="D268" s="15"/>
-      <c r="E268" s="15" t="s">
+      <c r="C268" s="9"/>
+      <c r="D268" s="9"/>
+      <c r="E268" s="9" t="s">
         <v>775</v>
       </c>
       <c r="F268" s="9"/>
       <c r="G268" s="9"/>
       <c r="H268" s="9"/>
-      <c r="I268" s="15" t="s">
+      <c r="I268" s="9" t="s">
         <v>776</v>
       </c>
-      <c r="J268" s="15" t="s">
+      <c r="J268" s="9" t="s">
         <v>777</v>
       </c>
     </row>
@@ -14023,21 +14074,21 @@
       <c r="A269" s="6">
         <v>229.6</v>
       </c>
-      <c r="B269" s="14" t="s">
+      <c r="B269" s="7" t="s">
         <v>778</v>
       </c>
-      <c r="C269" s="15"/>
-      <c r="D269" s="15"/>
-      <c r="E269" s="15" t="s">
+      <c r="C269" s="9"/>
+      <c r="D269" s="9"/>
+      <c r="E269" s="9" t="s">
         <v>779</v>
       </c>
       <c r="F269" s="9"/>
       <c r="G269" s="9"/>
       <c r="H269" s="9"/>
-      <c r="I269" s="15" t="s">
+      <c r="I269" s="9" t="s">
         <v>780</v>
       </c>
-      <c r="J269" s="15" t="s">
+      <c r="J269" s="9" t="s">
         <v>781</v>
       </c>
     </row>
@@ -14045,21 +14096,21 @@
       <c r="A270" s="6">
         <v>229.7</v>
       </c>
-      <c r="B270" s="14" t="s">
+      <c r="B270" s="7" t="s">
         <v>782</v>
       </c>
-      <c r="C270" s="15"/>
-      <c r="D270" s="15"/>
-      <c r="E270" s="15" t="s">
+      <c r="C270" s="9"/>
+      <c r="D270" s="9"/>
+      <c r="E270" s="9" t="s">
         <v>783</v>
       </c>
       <c r="F270" s="9"/>
       <c r="G270" s="9"/>
       <c r="H270" s="9"/>
-      <c r="I270" s="15" t="s">
+      <c r="I270" s="9" t="s">
         <v>765</v>
       </c>
-      <c r="J270" s="15" t="s">
+      <c r="J270" s="9" t="s">
         <v>784</v>
       </c>
     </row>
@@ -14067,21 +14118,21 @@
       <c r="A271" s="6">
         <v>230</v>
       </c>
-      <c r="B271" s="14" t="s">
+      <c r="B271" s="7" t="s">
         <v>785</v>
       </c>
-      <c r="C271" s="15"/>
-      <c r="D271" s="15"/>
-      <c r="E271" s="15" t="s">
+      <c r="C271" s="9"/>
+      <c r="D271" s="9"/>
+      <c r="E271" s="9" t="s">
         <v>786</v>
       </c>
-      <c r="F271" s="15"/>
-      <c r="G271" s="15"/>
+      <c r="F271" s="9"/>
+      <c r="G271" s="9"/>
       <c r="H271" s="9"/>
-      <c r="I271" s="15" t="s">
+      <c r="I271" s="9" t="s">
         <v>787</v>
       </c>
-      <c r="J271" s="15" t="s">
+      <c r="J271" s="9" t="s">
         <v>788</v>
       </c>
     </row>
@@ -14089,23 +14140,23 @@
       <c r="A272" s="6">
         <v>231</v>
       </c>
-      <c r="B272" s="14" t="s">
+      <c r="B272" s="7" t="s">
         <v>789</v>
       </c>
-      <c r="C272" s="15"/>
-      <c r="D272" s="15"/>
-      <c r="E272" s="15" t="s">
+      <c r="C272" s="9"/>
+      <c r="D272" s="9"/>
+      <c r="E272" s="9" t="s">
         <v>790</v>
       </c>
-      <c r="F272" s="15" t="s">
+      <c r="F272" s="9" t="s">
         <v>791</v>
       </c>
-      <c r="G272" s="15"/>
+      <c r="G272" s="9"/>
       <c r="H272" s="9"/>
-      <c r="I272" s="15" t="s">
+      <c r="I272" s="9" t="s">
         <v>792</v>
       </c>
-      <c r="J272" s="15" t="s">
+      <c r="J272" s="9" t="s">
         <v>793</v>
       </c>
     </row>
@@ -14113,21 +14164,21 @@
       <c r="A273" s="6">
         <v>232</v>
       </c>
-      <c r="B273" s="14" t="s">
+      <c r="B273" s="7" t="s">
         <v>794</v>
       </c>
-      <c r="C273" s="15"/>
-      <c r="D273" s="15"/>
-      <c r="E273" s="15" t="s">
+      <c r="C273" s="9"/>
+      <c r="D273" s="9"/>
+      <c r="E273" s="9" t="s">
         <v>795</v>
       </c>
-      <c r="F273" s="15"/>
-      <c r="G273" s="15"/>
+      <c r="F273" s="9"/>
+      <c r="G273" s="9"/>
       <c r="H273" s="9"/>
-      <c r="I273" s="15" t="s">
+      <c r="I273" s="9" t="s">
         <v>796</v>
       </c>
-      <c r="J273" s="15" t="s">
+      <c r="J273" s="9" t="s">
         <v>797</v>
       </c>
     </row>
@@ -14135,23 +14186,23 @@
       <c r="A274" s="6">
         <v>233</v>
       </c>
-      <c r="B274" s="14" t="s">
+      <c r="B274" s="7" t="s">
         <v>798</v>
       </c>
-      <c r="C274" s="15"/>
-      <c r="D274" s="15"/>
-      <c r="E274" s="15" t="s">
+      <c r="C274" s="9"/>
+      <c r="D274" s="9"/>
+      <c r="E274" s="9" t="s">
         <v>799</v>
       </c>
-      <c r="F274" s="15" t="s">
+      <c r="F274" s="9" t="s">
         <v>337</v>
       </c>
-      <c r="G274" s="15"/>
+      <c r="G274" s="9"/>
       <c r="H274" s="9"/>
-      <c r="I274" s="15" t="s">
+      <c r="I274" s="9" t="s">
         <v>800</v>
       </c>
-      <c r="J274" s="15" t="s">
+      <c r="J274" s="9" t="s">
         <v>801</v>
       </c>
     </row>
@@ -14159,23 +14210,23 @@
       <c r="A275" s="6">
         <v>234</v>
       </c>
-      <c r="B275" s="14" t="s">
+      <c r="B275" s="7" t="s">
         <v>802</v>
       </c>
-      <c r="C275" s="15"/>
-      <c r="D275" s="15"/>
-      <c r="E275" s="15" t="s">
+      <c r="C275" s="9"/>
+      <c r="D275" s="9"/>
+      <c r="E275" s="9" t="s">
         <v>803</v>
       </c>
-      <c r="F275" s="15" t="s">
+      <c r="F275" s="9" t="s">
         <v>337</v>
       </c>
-      <c r="G275" s="15"/>
+      <c r="G275" s="9"/>
       <c r="H275" s="9"/>
-      <c r="I275" s="15" t="s">
+      <c r="I275" s="9" t="s">
         <v>804</v>
       </c>
-      <c r="J275" s="15" t="s">
+      <c r="J275" s="9" t="s">
         <v>805</v>
       </c>
     </row>
@@ -14183,12 +14234,12 @@
       <c r="A276" s="6">
         <v>235</v>
       </c>
-      <c r="B276" s="14" t="s">
+      <c r="B276" s="7" t="s">
         <v>806</v>
       </c>
-      <c r="C276" s="15"/>
-      <c r="D276" s="15"/>
-      <c r="E276" s="15" t="s">
+      <c r="C276" s="9"/>
+      <c r="D276" s="9"/>
+      <c r="E276" s="9" t="s">
         <v>807</v>
       </c>
       <c r="F276" s="9" t="s">
@@ -14198,10 +14249,10 @@
         <v>641</v>
       </c>
       <c r="H276" s="9"/>
-      <c r="I276" s="15" t="s">
+      <c r="I276" s="9" t="s">
         <v>809</v>
       </c>
-      <c r="J276" s="15" t="s">
+      <c r="J276" s="9" t="s">
         <v>788</v>
       </c>
     </row>
@@ -14209,21 +14260,21 @@
       <c r="A277" s="6">
         <v>236</v>
       </c>
-      <c r="B277" s="14" t="s">
+      <c r="B277" s="7" t="s">
         <v>810</v>
       </c>
-      <c r="C277" s="15"/>
-      <c r="D277" s="15"/>
-      <c r="E277" s="15" t="s">
+      <c r="C277" s="9"/>
+      <c r="D277" s="9"/>
+      <c r="E277" s="9" t="s">
         <v>811</v>
       </c>
-      <c r="F277" s="15"/>
-      <c r="G277" s="15"/>
+      <c r="F277" s="9"/>
+      <c r="G277" s="9"/>
       <c r="H277" s="9"/>
-      <c r="I277" s="15" t="s">
+      <c r="I277" s="9" t="s">
         <v>812</v>
       </c>
-      <c r="J277" s="15" t="s">
+      <c r="J277" s="9" t="s">
         <v>813</v>
       </c>
     </row>
@@ -14231,21 +14282,21 @@
       <c r="A278" s="6">
         <v>237</v>
       </c>
-      <c r="B278" s="14" t="s">
+      <c r="B278" s="7" t="s">
         <v>814</v>
       </c>
-      <c r="C278" s="15"/>
-      <c r="D278" s="15"/>
-      <c r="E278" s="15" t="s">
+      <c r="C278" s="9"/>
+      <c r="D278" s="9"/>
+      <c r="E278" s="9" t="s">
         <v>811</v>
       </c>
-      <c r="F278" s="15"/>
-      <c r="G278" s="15"/>
+      <c r="F278" s="9"/>
+      <c r="G278" s="9"/>
       <c r="H278" s="9"/>
-      <c r="I278" s="15" t="s">
+      <c r="I278" s="9" t="s">
         <v>815</v>
       </c>
-      <c r="J278" s="15" t="s">
+      <c r="J278" s="9" t="s">
         <v>816</v>
       </c>
     </row>
@@ -14253,18 +14304,18 @@
       <c r="A279" s="6">
         <v>238</v>
       </c>
-      <c r="B279" s="14" t="s">
+      <c r="B279" s="7" t="s">
         <v>817</v>
       </c>
-      <c r="C279" s="15"/>
-      <c r="D279" s="15"/>
-      <c r="E279" s="15" t="s">
+      <c r="C279" s="9"/>
+      <c r="D279" s="9"/>
+      <c r="E279" s="9" t="s">
         <v>818</v>
       </c>
-      <c r="F279" s="15"/>
-      <c r="G279" s="15"/>
+      <c r="F279" s="9"/>
+      <c r="G279" s="9"/>
       <c r="H279" s="9"/>
-      <c r="I279" s="15" t="s">
+      <c r="I279" s="9" t="s">
         <v>819</v>
       </c>
       <c r="J279" s="9" t="s">
@@ -14275,23 +14326,23 @@
       <c r="A280" s="6">
         <v>239</v>
       </c>
-      <c r="B280" s="14" t="s">
+      <c r="B280" s="7" t="s">
         <v>821</v>
       </c>
-      <c r="C280" s="15"/>
-      <c r="D280" s="15"/>
-      <c r="E280" s="15" t="s">
+      <c r="C280" s="9"/>
+      <c r="D280" s="9"/>
+      <c r="E280" s="9" t="s">
         <v>822</v>
       </c>
-      <c r="F280" s="15" t="s">
+      <c r="F280" s="9" t="s">
         <v>791</v>
       </c>
-      <c r="G280" s="15"/>
+      <c r="G280" s="9"/>
       <c r="H280" s="9"/>
-      <c r="I280" s="15" t="s">
+      <c r="I280" s="9" t="s">
         <v>823</v>
       </c>
-      <c r="J280" s="15" t="s">
+      <c r="J280" s="9" t="s">
         <v>788</v>
       </c>
     </row>
@@ -14299,23 +14350,23 @@
       <c r="A281" s="6">
         <v>240</v>
       </c>
-      <c r="B281" s="14" t="s">
+      <c r="B281" s="7" t="s">
         <v>824</v>
       </c>
-      <c r="C281" s="15"/>
-      <c r="D281" s="15"/>
-      <c r="E281" s="15" t="s">
+      <c r="C281" s="9"/>
+      <c r="D281" s="9"/>
+      <c r="E281" s="9" t="s">
         <v>825</v>
       </c>
-      <c r="F281" s="15" t="s">
+      <c r="F281" s="9" t="s">
         <v>791</v>
       </c>
-      <c r="G281" s="15"/>
+      <c r="G281" s="9"/>
       <c r="H281" s="9"/>
-      <c r="I281" s="15" t="s">
+      <c r="I281" s="9" t="s">
         <v>826</v>
       </c>
-      <c r="J281" s="15" t="s">
+      <c r="J281" s="9" t="s">
         <v>827</v>
       </c>
     </row>
@@ -14323,21 +14374,21 @@
       <c r="A282" s="6">
         <v>241</v>
       </c>
-      <c r="B282" s="14" t="s">
+      <c r="B282" s="7" t="s">
         <v>828</v>
       </c>
-      <c r="C282" s="15"/>
-      <c r="D282" s="15"/>
-      <c r="E282" s="15" t="s">
+      <c r="C282" s="9"/>
+      <c r="D282" s="9"/>
+      <c r="E282" s="9" t="s">
         <v>829</v>
       </c>
-      <c r="F282" s="15"/>
-      <c r="G282" s="15"/>
+      <c r="F282" s="9"/>
+      <c r="G282" s="9"/>
       <c r="H282" s="9"/>
-      <c r="I282" s="15" t="s">
+      <c r="I282" s="9" t="s">
         <v>830</v>
       </c>
-      <c r="J282" s="15" t="s">
+      <c r="J282" s="9" t="s">
         <v>831</v>
       </c>
     </row>
@@ -14345,23 +14396,23 @@
       <c r="A283" s="6">
         <v>242</v>
       </c>
-      <c r="B283" s="14" t="s">
+      <c r="B283" s="7" t="s">
         <v>832</v>
       </c>
-      <c r="C283" s="15"/>
-      <c r="D283" s="15"/>
-      <c r="E283" s="15" t="s">
+      <c r="C283" s="9"/>
+      <c r="D283" s="9"/>
+      <c r="E283" s="9" t="s">
         <v>833</v>
       </c>
-      <c r="F283" s="15" t="s">
+      <c r="F283" s="9" t="s">
         <v>791</v>
       </c>
-      <c r="G283" s="15"/>
+      <c r="G283" s="9"/>
       <c r="H283" s="9"/>
-      <c r="I283" s="15" t="s">
+      <c r="I283" s="9" t="s">
         <v>834</v>
       </c>
-      <c r="J283" s="15" t="s">
+      <c r="J283" s="9" t="s">
         <v>788</v>
       </c>
     </row>
@@ -14369,12 +14420,12 @@
       <c r="A284" s="6">
         <v>243</v>
       </c>
-      <c r="B284" s="14" t="s">
+      <c r="B284" s="7" t="s">
         <v>835</v>
       </c>
-      <c r="C284" s="15"/>
-      <c r="D284" s="15"/>
-      <c r="E284" s="15" t="s">
+      <c r="C284" s="9"/>
+      <c r="D284" s="9"/>
+      <c r="E284" s="9" t="s">
         <v>836</v>
       </c>
       <c r="F284" s="9" t="s">
@@ -14382,10 +14433,10 @@
       </c>
       <c r="G284" s="9"/>
       <c r="H284" s="9"/>
-      <c r="I284" s="15" t="s">
+      <c r="I284" s="9" t="s">
         <v>837</v>
       </c>
-      <c r="J284" s="16" t="s">
+      <c r="J284" s="11" t="s">
         <v>838</v>
       </c>
     </row>
@@ -14393,18 +14444,18 @@
       <c r="A285" s="6">
         <v>244</v>
       </c>
-      <c r="B285" s="14" t="s">
+      <c r="B285" s="7" t="s">
         <v>839</v>
       </c>
-      <c r="C285" s="15"/>
-      <c r="D285" s="15"/>
-      <c r="E285" s="15" t="s">
+      <c r="C285" s="9"/>
+      <c r="D285" s="9"/>
+      <c r="E285" s="9" t="s">
         <v>840</v>
       </c>
-      <c r="F285" s="15"/>
-      <c r="G285" s="15"/>
+      <c r="F285" s="9"/>
+      <c r="G285" s="9"/>
       <c r="H285" s="9"/>
-      <c r="I285" s="15" t="s">
+      <c r="I285" s="9" t="s">
         <v>841</v>
       </c>
       <c r="J285" s="9"/>
@@ -14413,18 +14464,18 @@
       <c r="A286" s="6">
         <v>245</v>
       </c>
-      <c r="B286" s="14" t="s">
+      <c r="B286" s="7" t="s">
         <v>842</v>
       </c>
-      <c r="C286" s="15"/>
-      <c r="D286" s="15"/>
-      <c r="E286" s="15" t="s">
+      <c r="C286" s="9"/>
+      <c r="D286" s="9"/>
+      <c r="E286" s="9" t="s">
         <v>843</v>
       </c>
-      <c r="F286" s="15"/>
-      <c r="G286" s="15"/>
+      <c r="F286" s="9"/>
+      <c r="G286" s="9"/>
       <c r="H286" s="9"/>
-      <c r="I286" s="15" t="s">
+      <c r="I286" s="9" t="s">
         <v>844</v>
       </c>
       <c r="J286" s="9"/>
@@ -14433,15 +14484,15 @@
       <c r="A287" s="6">
         <v>269</v>
       </c>
-      <c r="B287" s="14" t="s">
+      <c r="B287" s="7" t="s">
         <v>845</v>
       </c>
       <c r="C287" s="7"/>
       <c r="D287" s="7"/>
-      <c r="E287" s="15" t="s">
+      <c r="E287" s="9" t="s">
         <v>846</v>
       </c>
-      <c r="F287" s="15" t="s">
+      <c r="F287" s="9" t="s">
         <v>808</v>
       </c>
       <c r="G287" s="9" t="s">
@@ -14457,15 +14508,15 @@
       <c r="A288" s="6">
         <v>270</v>
       </c>
-      <c r="B288" s="14" t="s">
+      <c r="B288" s="7" t="s">
         <v>847</v>
       </c>
       <c r="C288" s="7"/>
       <c r="D288" s="7"/>
-      <c r="E288" s="15" t="s">
+      <c r="E288" s="9" t="s">
         <v>848</v>
       </c>
-      <c r="F288" s="15" t="s">
+      <c r="F288" s="9" t="s">
         <v>808</v>
       </c>
       <c r="G288" s="9" t="s">
@@ -14481,15 +14532,15 @@
       <c r="A289" s="6">
         <v>271</v>
       </c>
-      <c r="B289" s="14" t="s">
+      <c r="B289" s="7" t="s">
         <v>849</v>
       </c>
       <c r="C289" s="7"/>
       <c r="D289" s="7"/>
-      <c r="E289" s="15" t="s">
+      <c r="E289" s="9" t="s">
         <v>846</v>
       </c>
-      <c r="F289" s="15" t="s">
+      <c r="F289" s="9" t="s">
         <v>808</v>
       </c>
       <c r="G289" s="9" t="s">
@@ -14505,15 +14556,15 @@
       <c r="A290" s="6">
         <v>272</v>
       </c>
-      <c r="B290" s="14" t="s">
+      <c r="B290" s="7" t="s">
         <v>850</v>
       </c>
       <c r="C290" s="7"/>
       <c r="D290" s="7"/>
-      <c r="E290" s="15" t="s">
+      <c r="E290" s="9" t="s">
         <v>851</v>
       </c>
-      <c r="F290" s="15" t="s">
+      <c r="F290" s="9" t="s">
         <v>808</v>
       </c>
       <c r="G290" s="9" t="s">
@@ -14531,15 +14582,15 @@
       <c r="A291" s="6">
         <v>273</v>
       </c>
-      <c r="B291" s="14" t="s">
+      <c r="B291" s="7" t="s">
         <v>853</v>
       </c>
       <c r="C291" s="7"/>
       <c r="D291" s="7"/>
-      <c r="E291" s="15" t="s">
+      <c r="E291" s="9" t="s">
         <v>851</v>
       </c>
-      <c r="F291" s="15" t="s">
+      <c r="F291" s="9" t="s">
         <v>808</v>
       </c>
       <c r="G291" s="9" t="s">
@@ -14557,15 +14608,15 @@
       <c r="A292" s="6">
         <v>274</v>
       </c>
-      <c r="B292" s="14" t="s">
+      <c r="B292" s="7" t="s">
         <v>855</v>
       </c>
       <c r="C292" s="7"/>
       <c r="D292" s="7"/>
-      <c r="E292" s="15" t="s">
+      <c r="E292" s="9" t="s">
         <v>851</v>
       </c>
-      <c r="F292" s="15" t="s">
+      <c r="F292" s="9" t="s">
         <v>808</v>
       </c>
       <c r="G292" s="9" t="s">
@@ -14581,15 +14632,15 @@
       <c r="A293" s="6">
         <v>275</v>
       </c>
-      <c r="B293" s="14" t="s">
+      <c r="B293" s="7" t="s">
         <v>856</v>
       </c>
       <c r="C293" s="7"/>
       <c r="D293" s="7"/>
-      <c r="E293" s="15" t="s">
+      <c r="E293" s="9" t="s">
         <v>846</v>
       </c>
-      <c r="F293" s="15" t="s">
+      <c r="F293" s="9" t="s">
         <v>808</v>
       </c>
       <c r="G293" s="9" t="s">
@@ -14605,15 +14656,15 @@
       <c r="A294" s="6">
         <v>276</v>
       </c>
-      <c r="B294" s="14" t="s">
+      <c r="B294" s="7" t="s">
         <v>857</v>
       </c>
       <c r="C294" s="7"/>
       <c r="D294" s="7"/>
-      <c r="E294" s="15" t="s">
+      <c r="E294" s="9" t="s">
         <v>858</v>
       </c>
-      <c r="F294" s="15" t="s">
+      <c r="F294" s="9" t="s">
         <v>808</v>
       </c>
       <c r="G294" s="9" t="s">
@@ -14629,15 +14680,15 @@
       <c r="A295" s="6">
         <v>277</v>
       </c>
-      <c r="B295" s="14" t="s">
+      <c r="B295" s="7" t="s">
         <v>859</v>
       </c>
       <c r="C295" s="7"/>
       <c r="D295" s="7"/>
-      <c r="E295" s="15" t="s">
+      <c r="E295" s="9" t="s">
         <v>860</v>
       </c>
-      <c r="F295" s="15" t="s">
+      <c r="F295" s="9" t="s">
         <v>808</v>
       </c>
       <c r="G295" s="9" t="s">
@@ -14653,12 +14704,12 @@
       <c r="A296" s="6">
         <v>278</v>
       </c>
-      <c r="B296" s="14" t="s">
+      <c r="B296" s="7" t="s">
         <v>861</v>
       </c>
       <c r="C296" s="7"/>
       <c r="D296" s="9"/>
-      <c r="E296" s="15" t="s">
+      <c r="E296" s="9" t="s">
         <v>862</v>
       </c>
       <c r="F296" s="9" t="s">
@@ -14666,10 +14717,10 @@
       </c>
       <c r="G296" s="9"/>
       <c r="H296" s="9"/>
-      <c r="I296" s="15" t="s">
+      <c r="I296" s="9" t="s">
         <v>864</v>
       </c>
-      <c r="J296" s="15" t="s">
+      <c r="J296" s="9" t="s">
         <v>865</v>
       </c>
     </row>
@@ -14677,12 +14728,12 @@
       <c r="A297" s="6">
         <v>279</v>
       </c>
-      <c r="B297" s="14" t="s">
+      <c r="B297" s="7" t="s">
         <v>866</v>
       </c>
       <c r="C297" s="7"/>
       <c r="D297" s="9"/>
-      <c r="E297" s="15" t="s">
+      <c r="E297" s="9" t="s">
         <v>867</v>
       </c>
       <c r="F297" s="9" t="s">
@@ -14690,10 +14741,10 @@
       </c>
       <c r="G297" s="9"/>
       <c r="H297" s="9"/>
-      <c r="I297" s="15" t="s">
+      <c r="I297" s="9" t="s">
         <v>868</v>
       </c>
-      <c r="J297" s="15" t="s">
+      <c r="J297" s="9" t="s">
         <v>865</v>
       </c>
     </row>
@@ -14701,12 +14752,12 @@
       <c r="A298" s="6">
         <v>280</v>
       </c>
-      <c r="B298" s="14" t="s">
+      <c r="B298" s="7" t="s">
         <v>869</v>
       </c>
       <c r="C298" s="7"/>
       <c r="D298" s="9"/>
-      <c r="E298" s="15" t="s">
+      <c r="E298" s="9" t="s">
         <v>862</v>
       </c>
       <c r="F298" s="9" t="s">
@@ -14714,10 +14765,10 @@
       </c>
       <c r="G298" s="9"/>
       <c r="H298" s="9"/>
-      <c r="I298" s="15" t="s">
+      <c r="I298" s="9" t="s">
         <v>870</v>
       </c>
-      <c r="J298" s="15" t="s">
+      <c r="J298" s="9" t="s">
         <v>871</v>
       </c>
     </row>
@@ -14725,12 +14776,12 @@
       <c r="A299" s="6">
         <v>281</v>
       </c>
-      <c r="B299" s="14" t="s">
+      <c r="B299" s="7" t="s">
         <v>872</v>
       </c>
       <c r="C299" s="7"/>
       <c r="D299" s="9"/>
-      <c r="E299" s="15" t="s">
+      <c r="E299" s="9" t="s">
         <v>862</v>
       </c>
       <c r="F299" s="9" t="s">
@@ -14738,10 +14789,10 @@
       </c>
       <c r="G299" s="9"/>
       <c r="H299" s="9"/>
-      <c r="I299" s="15" t="s">
+      <c r="I299" s="9" t="s">
         <v>873</v>
       </c>
-      <c r="J299" s="15" t="s">
+      <c r="J299" s="9" t="s">
         <v>874</v>
       </c>
     </row>
@@ -14749,12 +14800,12 @@
       <c r="A300" s="6">
         <v>282</v>
       </c>
-      <c r="B300" s="14" t="s">
+      <c r="B300" s="7" t="s">
         <v>875</v>
       </c>
       <c r="C300" s="7"/>
       <c r="D300" s="9"/>
-      <c r="E300" s="15" t="s">
+      <c r="E300" s="9" t="s">
         <v>862</v>
       </c>
       <c r="F300" s="9" t="s">
@@ -14762,21 +14813,21 @@
       </c>
       <c r="G300" s="9"/>
       <c r="H300" s="9"/>
-      <c r="I300" s="15" t="s">
+      <c r="I300" s="9" t="s">
         <v>876</v>
       </c>
-      <c r="J300" s="15"/>
+      <c r="J300" s="9"/>
     </row>
     <row r="301" s="2" customFormat="1" customHeight="1" spans="1:10">
       <c r="A301" s="6">
         <v>283</v>
       </c>
-      <c r="B301" s="14" t="s">
+      <c r="B301" s="7" t="s">
         <v>877</v>
       </c>
       <c r="C301" s="7"/>
       <c r="D301" s="9"/>
-      <c r="E301" s="15" t="s">
+      <c r="E301" s="9" t="s">
         <v>862</v>
       </c>
       <c r="F301" s="9" t="s">
@@ -14784,10 +14835,10 @@
       </c>
       <c r="G301" s="9"/>
       <c r="H301" s="9"/>
-      <c r="I301" s="15" t="s">
+      <c r="I301" s="9" t="s">
         <v>878</v>
       </c>
-      <c r="J301" s="15" t="s">
+      <c r="J301" s="9" t="s">
         <v>879</v>
       </c>
     </row>
@@ -14928,7 +14979,7 @@
       <c r="B307" s="7" t="s">
         <v>897</v>
       </c>
-      <c r="C307" s="17" t="s">
+      <c r="C307" s="14" t="s">
         <v>898</v>
       </c>
       <c r="D307" s="7"/>
@@ -14956,7 +15007,7 @@
       <c r="B308" s="7" t="s">
         <v>902</v>
       </c>
-      <c r="C308" s="17" t="s">
+      <c r="C308" s="14" t="s">
         <v>903</v>
       </c>
       <c r="D308" s="7"/>
@@ -14984,7 +15035,7 @@
       <c r="B309" s="7" t="s">
         <v>906</v>
       </c>
-      <c r="C309" s="17" t="s">
+      <c r="C309" s="14" t="s">
         <v>907</v>
       </c>
       <c r="D309" s="7"/>
@@ -15012,7 +15063,7 @@
       <c r="B310" s="7" t="s">
         <v>910</v>
       </c>
-      <c r="C310" s="17" t="s">
+      <c r="C310" s="14" t="s">
         <v>911</v>
       </c>
       <c r="D310" s="7"/>
@@ -15040,7 +15091,7 @@
       <c r="B311" s="7" t="s">
         <v>914</v>
       </c>
-      <c r="C311" s="17" t="s">
+      <c r="C311" s="14" t="s">
         <v>915</v>
       </c>
       <c r="D311" s="7"/>
@@ -15068,7 +15119,7 @@
       <c r="B312" s="7" t="s">
         <v>918</v>
       </c>
-      <c r="C312" s="17" t="s">
+      <c r="C312" s="14" t="s">
         <v>919</v>
       </c>
       <c r="D312" s="7"/>
@@ -15456,7 +15507,7 @@
       <c r="B327" s="7" t="s">
         <v>967</v>
       </c>
-      <c r="C327" s="17" t="s">
+      <c r="C327" s="14" t="s">
         <v>968</v>
       </c>
       <c r="D327" s="7"/>
@@ -15484,7 +15535,7 @@
       <c r="B328" s="7" t="s">
         <v>971</v>
       </c>
-      <c r="C328" s="17" t="s">
+      <c r="C328" s="14" t="s">
         <v>972</v>
       </c>
       <c r="D328" s="7"/>
@@ -15512,7 +15563,7 @@
       <c r="B329" s="7" t="s">
         <v>975</v>
       </c>
-      <c r="C329" s="17" t="s">
+      <c r="C329" s="14" t="s">
         <v>976</v>
       </c>
       <c r="D329" s="7"/>
@@ -15540,7 +15591,7 @@
       <c r="B330" s="7" t="s">
         <v>979</v>
       </c>
-      <c r="C330" s="17" t="s">
+      <c r="C330" s="14" t="s">
         <v>980</v>
       </c>
       <c r="D330" s="7"/>
@@ -15568,7 +15619,7 @@
       <c r="B331" s="7" t="s">
         <v>983</v>
       </c>
-      <c r="C331" s="17" t="s">
+      <c r="C331" s="14" t="s">
         <v>984</v>
       </c>
       <c r="D331" s="7"/>
@@ -15596,7 +15647,7 @@
       <c r="B332" s="7" t="s">
         <v>987</v>
       </c>
-      <c r="C332" s="17" t="s">
+      <c r="C332" s="14" t="s">
         <v>988</v>
       </c>
       <c r="D332" s="7"/>
@@ -15624,7 +15675,7 @@
       <c r="B333" s="7" t="s">
         <v>991</v>
       </c>
-      <c r="C333" s="17" t="s">
+      <c r="C333" s="14" t="s">
         <v>992</v>
       </c>
       <c r="D333" s="7"/>
@@ -15654,7 +15705,7 @@
       <c r="B334" s="7" t="s">
         <v>996</v>
       </c>
-      <c r="C334" s="17" t="s">
+      <c r="C334" s="14" t="s">
         <v>997</v>
       </c>
       <c r="D334" s="7"/>
@@ -15684,7 +15735,7 @@
       <c r="B335" s="7" t="s">
         <v>999</v>
       </c>
-      <c r="C335" s="17" t="s">
+      <c r="C335" s="14" t="s">
         <v>1000</v>
       </c>
       <c r="D335" s="7"/>
@@ -15714,7 +15765,7 @@
       <c r="B336" s="7" t="s">
         <v>1002</v>
       </c>
-      <c r="C336" s="17" t="s">
+      <c r="C336" s="14" t="s">
         <v>1003</v>
       </c>
       <c r="D336" s="7"/>
@@ -15742,7 +15793,7 @@
       <c r="B337" s="7" t="s">
         <v>1005</v>
       </c>
-      <c r="C337" s="17" t="s">
+      <c r="C337" s="14" t="s">
         <v>1006</v>
       </c>
       <c r="D337" s="7"/>
@@ -15772,7 +15823,7 @@
       <c r="B338" s="7" t="s">
         <v>1009</v>
       </c>
-      <c r="C338" s="17" t="s">
+      <c r="C338" s="14" t="s">
         <v>1010</v>
       </c>
       <c r="D338" s="7"/>
@@ -15830,7 +15881,7 @@
       <c r="B340" s="7" t="s">
         <v>1017</v>
       </c>
-      <c r="C340" s="17" t="s">
+      <c r="C340" s="14" t="s">
         <v>1018</v>
       </c>
       <c r="D340" s="7"/>
@@ -15860,7 +15911,7 @@
       <c r="B341" s="7" t="s">
         <v>1020</v>
       </c>
-      <c r="C341" s="17" t="s">
+      <c r="C341" s="14" t="s">
         <v>1021</v>
       </c>
       <c r="D341" s="7"/>
@@ -15890,7 +15941,7 @@
       <c r="B342" s="7" t="s">
         <v>1023</v>
       </c>
-      <c r="C342" s="17" t="s">
+      <c r="C342" s="14" t="s">
         <v>1024</v>
       </c>
       <c r="D342" s="7"/>
@@ -15920,7 +15971,7 @@
       <c r="B343" s="7" t="s">
         <v>1026</v>
       </c>
-      <c r="C343" s="17" t="s">
+      <c r="C343" s="14" t="s">
         <v>1027</v>
       </c>
       <c r="D343" s="7"/>
@@ -15950,7 +16001,7 @@
       <c r="B344" s="7" t="s">
         <v>1030</v>
       </c>
-      <c r="C344" s="17" t="s">
+      <c r="C344" s="14" t="s">
         <v>1031</v>
       </c>
       <c r="D344" s="7"/>
@@ -15980,7 +16031,7 @@
       <c r="B345" s="7" t="s">
         <v>1033</v>
       </c>
-      <c r="C345" s="17" t="s">
+      <c r="C345" s="14" t="s">
         <v>1034</v>
       </c>
       <c r="D345" s="7"/>
@@ -16010,7 +16061,7 @@
       <c r="B346" s="7" t="s">
         <v>1036</v>
       </c>
-      <c r="C346" s="17" t="s">
+      <c r="C346" s="14" t="s">
         <v>1037</v>
       </c>
       <c r="D346" s="7"/>
@@ -16040,7 +16091,7 @@
       <c r="B347" s="7" t="s">
         <v>1040</v>
       </c>
-      <c r="C347" s="17" t="s">
+      <c r="C347" s="14" t="s">
         <v>1041</v>
       </c>
       <c r="D347" s="7"/>
@@ -16070,7 +16121,7 @@
       <c r="B348" s="7" t="s">
         <v>1044</v>
       </c>
-      <c r="C348" s="17" t="s">
+      <c r="C348" s="14" t="s">
         <v>1045</v>
       </c>
       <c r="D348" s="7"/>
@@ -16100,7 +16151,7 @@
       <c r="B349" s="7" t="s">
         <v>1048</v>
       </c>
-      <c r="C349" s="17" t="s">
+      <c r="C349" s="14" t="s">
         <v>1049</v>
       </c>
       <c r="D349" s="7"/>
@@ -16130,7 +16181,7 @@
       <c r="B350" s="7" t="s">
         <v>1052</v>
       </c>
-      <c r="C350" s="17" t="s">
+      <c r="C350" s="14" t="s">
         <v>1053</v>
       </c>
       <c r="D350" s="7"/>
@@ -16160,7 +16211,7 @@
       <c r="B351" s="7" t="s">
         <v>1056</v>
       </c>
-      <c r="C351" s="17" t="s">
+      <c r="C351" s="14" t="s">
         <v>1057</v>
       </c>
       <c r="D351" s="7"/>
@@ -17776,7 +17827,7 @@
       <c r="B414" s="7" t="s">
         <v>1256</v>
       </c>
-      <c r="C414" s="17" t="s">
+      <c r="C414" s="14" t="s">
         <v>1257</v>
       </c>
       <c r="D414" s="7"/>
@@ -17804,7 +17855,7 @@
       <c r="B415" s="7" t="s">
         <v>1259</v>
       </c>
-      <c r="C415" s="17" t="s">
+      <c r="C415" s="14" t="s">
         <v>1260</v>
       </c>
       <c r="D415" s="7"/>
@@ -17832,7 +17883,7 @@
       <c r="B416" s="7" t="s">
         <v>1263</v>
       </c>
-      <c r="C416" s="17" t="s">
+      <c r="C416" s="14" t="s">
         <v>1264</v>
       </c>
       <c r="D416" s="7"/>
@@ -17860,7 +17911,7 @@
       <c r="B417" s="7" t="s">
         <v>1267</v>
       </c>
-      <c r="C417" s="17" t="s">
+      <c r="C417" s="14" t="s">
         <v>1268</v>
       </c>
       <c r="D417" s="7"/>
@@ -17888,7 +17939,7 @@
       <c r="B418" s="7" t="s">
         <v>1271</v>
       </c>
-      <c r="C418" s="17" t="s">
+      <c r="C418" s="14" t="s">
         <v>1272</v>
       </c>
       <c r="D418" s="7"/>
@@ -17916,7 +17967,7 @@
       <c r="B419" s="7" t="s">
         <v>1275</v>
       </c>
-      <c r="C419" s="17" t="s">
+      <c r="C419" s="14" t="s">
         <v>1276</v>
       </c>
       <c r="D419" s="7"/>
@@ -17944,7 +17995,7 @@
       <c r="B420" s="7" t="s">
         <v>1278</v>
       </c>
-      <c r="C420" s="17" t="s">
+      <c r="C420" s="14" t="s">
         <v>1279</v>
       </c>
       <c r="D420" s="7"/>
@@ -17970,7 +18021,7 @@
       <c r="B421" s="7" t="s">
         <v>1281</v>
       </c>
-      <c r="C421" s="17" t="s">
+      <c r="C421" s="14" t="s">
         <v>1282</v>
       </c>
       <c r="D421" s="7"/>
@@ -17996,7 +18047,7 @@
       <c r="B422" s="7" t="s">
         <v>1284</v>
       </c>
-      <c r="C422" s="17" t="s">
+      <c r="C422" s="14" t="s">
         <v>1285</v>
       </c>
       <c r="D422" s="7"/>
@@ -18046,7 +18097,7 @@
       <c r="B424" s="7" t="s">
         <v>1290</v>
       </c>
-      <c r="C424" s="17" t="s">
+      <c r="C424" s="14" t="s">
         <v>1291</v>
       </c>
       <c r="D424" s="7"/>
@@ -18074,7 +18125,7 @@
       <c r="B425" s="7" t="s">
         <v>1293</v>
       </c>
-      <c r="C425" s="17" t="s">
+      <c r="C425" s="14" t="s">
         <v>1294</v>
       </c>
       <c r="D425" s="7"/>
@@ -18102,7 +18153,7 @@
       <c r="B426" s="7" t="s">
         <v>1296</v>
       </c>
-      <c r="C426" s="17" t="s">
+      <c r="C426" s="14" t="s">
         <v>1297</v>
       </c>
       <c r="D426" s="7"/>
@@ -18130,7 +18181,7 @@
       <c r="B427" s="7" t="s">
         <v>1299</v>
       </c>
-      <c r="C427" s="17" t="s">
+      <c r="C427" s="14" t="s">
         <v>1300</v>
       </c>
       <c r="D427" s="7"/>
@@ -18158,7 +18209,7 @@
       <c r="B428" s="7" t="s">
         <v>1303</v>
       </c>
-      <c r="C428" s="17" t="s">
+      <c r="C428" s="14" t="s">
         <v>1304</v>
       </c>
       <c r="D428" s="7"/>
@@ -18186,7 +18237,7 @@
       <c r="B429" s="7" t="s">
         <v>1306</v>
       </c>
-      <c r="C429" s="17" t="s">
+      <c r="C429" s="14" t="s">
         <v>1307</v>
       </c>
       <c r="D429" s="7"/>
@@ -18214,7 +18265,7 @@
       <c r="B430" s="7" t="s">
         <v>1309</v>
       </c>
-      <c r="C430" s="17" t="s">
+      <c r="C430" s="14" t="s">
         <v>1310</v>
       </c>
       <c r="D430" s="7"/>
@@ -18959,12 +19010,12 @@
       <c r="A460" s="6">
         <v>426</v>
       </c>
-      <c r="B460" s="14" t="s">
+      <c r="B460" s="7" t="s">
         <v>1389</v>
       </c>
       <c r="C460" s="7"/>
       <c r="D460" s="9"/>
-      <c r="E460" s="15" t="s">
+      <c r="E460" s="9" t="s">
         <v>1390</v>
       </c>
       <c r="F460" s="7" t="s">
@@ -18977,7 +19028,7 @@
         <v>1391</v>
       </c>
       <c r="I460" s="9"/>
-      <c r="J460" s="16" t="s">
+      <c r="J460" s="11" t="s">
         <v>1122</v>
       </c>
     </row>
@@ -18985,12 +19036,12 @@
       <c r="A461" s="6">
         <v>427</v>
       </c>
-      <c r="B461" s="14" t="s">
+      <c r="B461" s="7" t="s">
         <v>1392</v>
       </c>
       <c r="C461" s="7"/>
       <c r="D461" s="9"/>
-      <c r="E461" s="15" t="s">
+      <c r="E461" s="9" t="s">
         <v>1390</v>
       </c>
       <c r="F461" s="7" t="s">
@@ -19003,7 +19054,7 @@
         <v>1393</v>
       </c>
       <c r="I461" s="9"/>
-      <c r="J461" s="16" t="s">
+      <c r="J461" s="11" t="s">
         <v>1125</v>
       </c>
     </row>
@@ -19011,12 +19062,12 @@
       <c r="A462" s="6">
         <v>428</v>
       </c>
-      <c r="B462" s="14" t="s">
+      <c r="B462" s="7" t="s">
         <v>1394</v>
       </c>
       <c r="C462" s="7"/>
       <c r="D462" s="9"/>
-      <c r="E462" s="15" t="s">
+      <c r="E462" s="9" t="s">
         <v>1390</v>
       </c>
       <c r="F462" s="7" t="s">
@@ -19029,7 +19080,7 @@
         <v>1395</v>
       </c>
       <c r="I462" s="9"/>
-      <c r="J462" s="16" t="s">
+      <c r="J462" s="11" t="s">
         <v>1128</v>
       </c>
     </row>
@@ -19037,12 +19088,12 @@
       <c r="A463" s="6">
         <v>429</v>
       </c>
-      <c r="B463" s="14" t="s">
+      <c r="B463" s="7" t="s">
         <v>1396</v>
       </c>
       <c r="C463" s="7"/>
       <c r="D463" s="9"/>
-      <c r="E463" s="15" t="s">
+      <c r="E463" s="9" t="s">
         <v>1390</v>
       </c>
       <c r="F463" s="7" t="s">
@@ -19055,7 +19106,7 @@
         <v>1397</v>
       </c>
       <c r="I463" s="9"/>
-      <c r="J463" s="16" t="s">
+      <c r="J463" s="11" t="s">
         <v>1398</v>
       </c>
     </row>
@@ -19063,12 +19114,12 @@
       <c r="A464" s="6">
         <v>430</v>
       </c>
-      <c r="B464" s="14" t="s">
+      <c r="B464" s="7" t="s">
         <v>1399</v>
       </c>
       <c r="C464" s="7"/>
       <c r="D464" s="9"/>
-      <c r="E464" s="15" t="s">
+      <c r="E464" s="9" t="s">
         <v>1390</v>
       </c>
       <c r="F464" s="7" t="s">
@@ -19081,7 +19132,7 @@
         <v>1400</v>
       </c>
       <c r="I464" s="9"/>
-      <c r="J464" s="16" t="s">
+      <c r="J464" s="11" t="s">
         <v>1401</v>
       </c>
     </row>
@@ -19089,12 +19140,12 @@
       <c r="A465" s="6">
         <v>431</v>
       </c>
-      <c r="B465" s="14" t="s">
+      <c r="B465" s="7" t="s">
         <v>1402</v>
       </c>
       <c r="C465" s="7"/>
       <c r="D465" s="9"/>
-      <c r="E465" s="15" t="s">
+      <c r="E465" s="9" t="s">
         <v>1390</v>
       </c>
       <c r="F465" s="7" t="s">
@@ -19107,7 +19158,7 @@
         <v>1404</v>
       </c>
       <c r="I465" s="9"/>
-      <c r="J465" s="16" t="s">
+      <c r="J465" s="11" t="s">
         <v>1405</v>
       </c>
     </row>
@@ -19115,12 +19166,12 @@
       <c r="A466" s="6">
         <v>432</v>
       </c>
-      <c r="B466" s="14" t="s">
+      <c r="B466" s="7" t="s">
         <v>1406</v>
       </c>
       <c r="C466" s="7"/>
       <c r="D466" s="9"/>
-      <c r="E466" s="15" t="s">
+      <c r="E466" s="9" t="s">
         <v>1390</v>
       </c>
       <c r="F466" s="7" t="s">
@@ -19135,7 +19186,7 @@
       <c r="I466" s="9" t="s">
         <v>1408</v>
       </c>
-      <c r="J466" s="16" t="s">
+      <c r="J466" s="11" t="s">
         <v>1409</v>
       </c>
     </row>
@@ -19143,12 +19194,12 @@
       <c r="A467" s="6">
         <v>433</v>
       </c>
-      <c r="B467" s="14" t="s">
+      <c r="B467" s="7" t="s">
         <v>1410</v>
       </c>
       <c r="C467" s="7"/>
       <c r="D467" s="9"/>
-      <c r="E467" s="15" t="s">
+      <c r="E467" s="9" t="s">
         <v>1390</v>
       </c>
       <c r="F467" s="7" t="s">
@@ -19163,7 +19214,7 @@
       <c r="I467" s="9" t="s">
         <v>1408</v>
       </c>
-      <c r="J467" s="16" t="s">
+      <c r="J467" s="11" t="s">
         <v>1413</v>
       </c>
     </row>
@@ -19171,12 +19222,12 @@
       <c r="A468" s="6">
         <v>434</v>
       </c>
-      <c r="B468" s="14" t="s">
+      <c r="B468" s="7" t="s">
         <v>1414</v>
       </c>
       <c r="C468" s="7"/>
       <c r="D468" s="9"/>
-      <c r="E468" s="15" t="s">
+      <c r="E468" s="9" t="s">
         <v>1390</v>
       </c>
       <c r="F468" s="7" t="s">
@@ -19191,7 +19242,7 @@
       <c r="I468" s="9" t="s">
         <v>1408</v>
       </c>
-      <c r="J468" s="16" t="s">
+      <c r="J468" s="11" t="s">
         <v>1122</v>
       </c>
     </row>
@@ -19199,12 +19250,12 @@
       <c r="A469" s="6">
         <v>435</v>
       </c>
-      <c r="B469" s="14" t="s">
+      <c r="B469" s="7" t="s">
         <v>1416</v>
       </c>
       <c r="C469" s="7"/>
       <c r="D469" s="9"/>
-      <c r="E469" s="15" t="s">
+      <c r="E469" s="9" t="s">
         <v>1417</v>
       </c>
       <c r="F469" s="7"/>
@@ -19215,7 +19266,7 @@
       <c r="I469" s="9" t="s">
         <v>1408</v>
       </c>
-      <c r="J469" s="16" t="s">
+      <c r="J469" s="11" t="s">
         <v>1419</v>
       </c>
     </row>
@@ -19223,12 +19274,12 @@
       <c r="A470" s="6">
         <v>436</v>
       </c>
-      <c r="B470" s="14" t="s">
+      <c r="B470" s="7" t="s">
         <v>1420</v>
       </c>
       <c r="C470" s="7"/>
       <c r="D470" s="9"/>
-      <c r="E470" s="15" t="s">
+      <c r="E470" s="9" t="s">
         <v>1390</v>
       </c>
       <c r="F470" s="7" t="s">
@@ -19243,7 +19294,7 @@
       <c r="I470" s="9" t="s">
         <v>1408</v>
       </c>
-      <c r="J470" s="16" t="s">
+      <c r="J470" s="11" t="s">
         <v>1128</v>
       </c>
     </row>
@@ -19251,12 +19302,12 @@
       <c r="A471" s="6">
         <v>437</v>
       </c>
-      <c r="B471" s="14" t="s">
+      <c r="B471" s="7" t="s">
         <v>1422</v>
       </c>
       <c r="C471" s="7"/>
       <c r="D471" s="9"/>
-      <c r="E471" s="15" t="s">
+      <c r="E471" s="9" t="s">
         <v>1390</v>
       </c>
       <c r="F471" s="7" t="s">
@@ -19271,7 +19322,7 @@
       <c r="I471" s="9" t="s">
         <v>1408</v>
       </c>
-      <c r="J471" s="16" t="s">
+      <c r="J471" s="11" t="s">
         <v>1398</v>
       </c>
     </row>
@@ -19279,12 +19330,12 @@
       <c r="A472" s="6">
         <v>438</v>
       </c>
-      <c r="B472" s="14" t="s">
+      <c r="B472" s="7" t="s">
         <v>1424</v>
       </c>
       <c r="C472" s="7"/>
       <c r="D472" s="9"/>
-      <c r="E472" s="15" t="s">
+      <c r="E472" s="9" t="s">
         <v>1390</v>
       </c>
       <c r="F472" s="7" t="s">
@@ -19299,7 +19350,7 @@
       <c r="I472" s="9" t="s">
         <v>1408</v>
       </c>
-      <c r="J472" s="16" t="s">
+      <c r="J472" s="11" t="s">
         <v>1401</v>
       </c>
     </row>
@@ -19307,12 +19358,12 @@
       <c r="A473" s="6">
         <v>439</v>
       </c>
-      <c r="B473" s="14" t="s">
+      <c r="B473" s="7" t="s">
         <v>1426</v>
       </c>
       <c r="C473" s="7"/>
       <c r="D473" s="9"/>
-      <c r="E473" s="15" t="s">
+      <c r="E473" s="9" t="s">
         <v>1390</v>
       </c>
       <c r="F473" s="7" t="s">
@@ -19327,7 +19378,7 @@
       <c r="I473" s="9" t="s">
         <v>1408</v>
       </c>
-      <c r="J473" s="16" t="s">
+      <c r="J473" s="11" t="s">
         <v>1405</v>
       </c>
     </row>
@@ -19335,12 +19386,12 @@
       <c r="A474" s="6">
         <v>440</v>
       </c>
-      <c r="B474" s="14" t="s">
+      <c r="B474" s="7" t="s">
         <v>1428</v>
       </c>
       <c r="C474" s="7"/>
       <c r="D474" s="9"/>
-      <c r="E474" s="15" t="s">
+      <c r="E474" s="9" t="s">
         <v>1390</v>
       </c>
       <c r="F474" s="7" t="s">
@@ -19355,7 +19406,7 @@
       <c r="I474" s="9" t="s">
         <v>1408</v>
       </c>
-      <c r="J474" s="16" t="s">
+      <c r="J474" s="11" t="s">
         <v>1409</v>
       </c>
     </row>
@@ -19363,12 +19414,12 @@
       <c r="A475" s="6">
         <v>441</v>
       </c>
-      <c r="B475" s="14" t="s">
+      <c r="B475" s="7" t="s">
         <v>1430</v>
       </c>
       <c r="C475" s="7"/>
       <c r="D475" s="9"/>
-      <c r="E475" s="15" t="s">
+      <c r="E475" s="9" t="s">
         <v>1390</v>
       </c>
       <c r="F475" s="7" t="s">
@@ -19383,7 +19434,7 @@
       <c r="I475" s="9" t="s">
         <v>1408</v>
       </c>
-      <c r="J475" s="16" t="s">
+      <c r="J475" s="11" t="s">
         <v>1413</v>
       </c>
     </row>
@@ -19391,12 +19442,12 @@
       <c r="A476" s="6">
         <v>442</v>
       </c>
-      <c r="B476" s="14" t="s">
+      <c r="B476" s="7" t="s">
         <v>1432</v>
       </c>
       <c r="C476" s="7"/>
       <c r="D476" s="9"/>
-      <c r="E476" s="15" t="s">
+      <c r="E476" s="9" t="s">
         <v>1433</v>
       </c>
       <c r="F476" s="7"/>
@@ -19413,12 +19464,12 @@
       <c r="A477" s="6">
         <v>443</v>
       </c>
-      <c r="B477" s="14" t="s">
+      <c r="B477" s="7" t="s">
         <v>1435</v>
       </c>
       <c r="C477" s="7"/>
       <c r="D477" s="9"/>
-      <c r="E477" s="15" t="s">
+      <c r="E477" s="9" t="s">
         <v>1436</v>
       </c>
       <c r="F477" s="7" t="s">
@@ -19439,20 +19490,20 @@
       <c r="A478" s="6">
         <v>444</v>
       </c>
-      <c r="B478" s="14" t="s">
+      <c r="B478" s="7" t="s">
         <v>1438</v>
       </c>
       <c r="C478" s="7"/>
       <c r="D478" s="9"/>
-      <c r="E478" s="15" t="s">
+      <c r="E478" s="9"/>
+      <c r="F478" s="7" t="s">
         <v>1439</v>
       </c>
-      <c r="F478" s="7" t="s">
+      <c r="G478" s="7" t="s">
+        <v>668</v>
+      </c>
+      <c r="H478" s="9" t="s">
         <v>1440</v>
-      </c>
-      <c r="G478" s="7"/>
-      <c r="H478" s="9" t="s">
-        <v>1441</v>
       </c>
       <c r="I478" s="9" t="s">
         <v>1408</v>
@@ -19463,12 +19514,12 @@
       <c r="A479" s="6">
         <v>445</v>
       </c>
-      <c r="B479" s="14" t="s">
-        <v>1442</v>
+      <c r="B479" s="7" t="s">
+        <v>1441</v>
       </c>
       <c r="C479" s="7"/>
       <c r="D479" s="9"/>
-      <c r="E479" s="15"/>
+      <c r="E479" s="9"/>
       <c r="F479" s="7" t="s">
         <v>952</v>
       </c>
@@ -19476,7 +19527,7 @@
         <v>668</v>
       </c>
       <c r="H479" s="9" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="I479" s="9" t="s">
         <v>1408</v>
@@ -19487,12 +19538,12 @@
       <c r="A480" s="6">
         <v>446</v>
       </c>
-      <c r="B480" s="14" t="s">
-        <v>1444</v>
+      <c r="B480" s="7" t="s">
+        <v>1443</v>
       </c>
       <c r="C480" s="7"/>
       <c r="D480" s="9"/>
-      <c r="E480" s="15"/>
+      <c r="E480" s="9"/>
       <c r="F480" s="7" t="s">
         <v>952</v>
       </c>
@@ -19500,25 +19551,25 @@
         <v>668</v>
       </c>
       <c r="H480" s="9" t="s">
+        <v>1444</v>
+      </c>
+      <c r="I480" s="9" t="s">
         <v>1445</v>
       </c>
-      <c r="I480" s="9" t="s">
+      <c r="J480" s="11" t="s">
         <v>1446</v>
-      </c>
-      <c r="J480" s="16" t="s">
-        <v>1447</v>
       </c>
     </row>
     <row r="481" s="2" customFormat="1" customHeight="1" spans="1:10">
       <c r="A481" s="6">
         <v>447</v>
       </c>
-      <c r="B481" s="14" t="s">
-        <v>1448</v>
+      <c r="B481" s="7" t="s">
+        <v>1447</v>
       </c>
       <c r="C481" s="7"/>
       <c r="D481" s="9"/>
-      <c r="E481" s="15"/>
+      <c r="E481" s="9"/>
       <c r="F481" s="7" t="s">
         <v>952</v>
       </c>
@@ -19526,7 +19577,7 @@
         <v>635</v>
       </c>
       <c r="H481" s="9" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="I481" s="9" t="s">
         <v>1408</v>
@@ -19537,13 +19588,13 @@
       <c r="A482" s="6">
         <v>448</v>
       </c>
-      <c r="B482" s="14" t="s">
-        <v>1450</v>
+      <c r="B482" s="7" t="s">
+        <v>1449</v>
       </c>
       <c r="C482" s="7"/>
       <c r="D482" s="9"/>
-      <c r="E482" s="15" t="s">
-        <v>1451</v>
+      <c r="E482" s="9" t="s">
+        <v>1450</v>
       </c>
       <c r="F482" s="7" t="s">
         <v>952</v>
@@ -19552,7 +19603,7 @@
         <v>635</v>
       </c>
       <c r="H482" s="9" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="I482" s="9" t="s">
         <v>1408</v>
@@ -19563,13 +19614,13 @@
       <c r="A483" s="6">
         <v>449</v>
       </c>
-      <c r="B483" s="14" t="s">
-        <v>1453</v>
+      <c r="B483" s="7" t="s">
+        <v>1452</v>
       </c>
       <c r="C483" s="7"/>
       <c r="D483" s="9"/>
-      <c r="E483" s="15" t="s">
-        <v>1454</v>
+      <c r="E483" s="9" t="s">
+        <v>1453</v>
       </c>
       <c r="F483" s="7" t="s">
         <v>952</v>
@@ -19578,7 +19629,7 @@
         <v>635</v>
       </c>
       <c r="H483" s="9" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="I483" s="9" t="s">
         <v>1408</v>
@@ -19589,20 +19640,20 @@
       <c r="A484" s="6">
         <v>450</v>
       </c>
-      <c r="B484" s="14" t="s">
-        <v>1456</v>
+      <c r="B484" s="7" t="s">
+        <v>1455</v>
       </c>
       <c r="C484" s="7"/>
       <c r="D484" s="9"/>
-      <c r="E484" s="15" t="s">
-        <v>1457</v>
-      </c>
+      <c r="E484" s="9"/>
       <c r="F484" s="7" t="s">
-        <v>1440</v>
-      </c>
-      <c r="G484" s="7"/>
+        <v>1439</v>
+      </c>
+      <c r="G484" s="7" t="s">
+        <v>641</v>
+      </c>
       <c r="H484" s="9" t="s">
-        <v>1458</v>
+        <v>1456</v>
       </c>
       <c r="I484" s="9" t="s">
         <v>1408</v>
@@ -19613,12 +19664,12 @@
       <c r="A485" s="6">
         <v>451</v>
       </c>
-      <c r="B485" s="14" t="s">
-        <v>1459</v>
+      <c r="B485" s="7" t="s">
+        <v>1457</v>
       </c>
       <c r="C485" s="7"/>
       <c r="D485" s="9"/>
-      <c r="E485" s="15"/>
+      <c r="E485" s="9"/>
       <c r="F485" s="7" t="s">
         <v>952</v>
       </c>
@@ -19626,7 +19677,7 @@
         <v>618</v>
       </c>
       <c r="H485" s="9" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="I485" s="9" t="s">
         <v>1408</v>
@@ -19637,12 +19688,12 @@
       <c r="A486" s="6">
         <v>452</v>
       </c>
-      <c r="B486" s="14" t="s">
-        <v>1461</v>
+      <c r="B486" s="7" t="s">
+        <v>1459</v>
       </c>
       <c r="C486" s="7"/>
       <c r="D486" s="9"/>
-      <c r="E486" s="15"/>
+      <c r="E486" s="9"/>
       <c r="F486" s="7" t="s">
         <v>952</v>
       </c>
@@ -19650,7 +19701,7 @@
         <v>618</v>
       </c>
       <c r="H486" s="9" t="s">
-        <v>1462</v>
+        <v>1460</v>
       </c>
       <c r="I486" s="9" t="s">
         <v>1408</v>
@@ -19661,12 +19712,12 @@
       <c r="A487" s="6">
         <v>453</v>
       </c>
-      <c r="B487" s="14" t="s">
-        <v>1463</v>
+      <c r="B487" s="7" t="s">
+        <v>1461</v>
       </c>
       <c r="C487" s="7"/>
       <c r="D487" s="9"/>
-      <c r="E487" s="15"/>
+      <c r="E487" s="9"/>
       <c r="F487" s="7" t="s">
         <v>952</v>
       </c>
@@ -19674,7 +19725,7 @@
         <v>618</v>
       </c>
       <c r="H487" s="9" t="s">
-        <v>1464</v>
+        <v>1462</v>
       </c>
       <c r="I487" s="9" t="s">
         <v>1408</v>
@@ -19685,20 +19736,20 @@
       <c r="A488" s="6">
         <v>454</v>
       </c>
-      <c r="B488" s="14" t="s">
-        <v>1465</v>
+      <c r="B488" s="7" t="s">
+        <v>1463</v>
       </c>
       <c r="C488" s="7"/>
       <c r="D488" s="9"/>
-      <c r="E488" s="15" t="s">
-        <v>1466</v>
-      </c>
+      <c r="E488" s="9"/>
       <c r="F488" s="7" t="s">
-        <v>1440</v>
-      </c>
-      <c r="G488" s="7"/>
+        <v>1439</v>
+      </c>
+      <c r="G488" s="7" t="s">
+        <v>638</v>
+      </c>
       <c r="H488" s="9" t="s">
-        <v>1467</v>
+        <v>1464</v>
       </c>
       <c r="I488" s="9" t="s">
         <v>1408</v>
@@ -19709,12 +19760,12 @@
       <c r="A489" s="6">
         <v>455</v>
       </c>
-      <c r="B489" s="14" t="s">
-        <v>1468</v>
+      <c r="B489" s="7" t="s">
+        <v>1465</v>
       </c>
       <c r="C489" s="7"/>
       <c r="D489" s="9"/>
-      <c r="E489" s="15"/>
+      <c r="E489" s="9"/>
       <c r="F489" s="7" t="s">
         <v>952</v>
       </c>
@@ -19722,7 +19773,7 @@
         <v>629</v>
       </c>
       <c r="H489" s="9" t="s">
-        <v>1469</v>
+        <v>1466</v>
       </c>
       <c r="I489" s="9" t="s">
         <v>1408</v>
@@ -19734,12 +19785,12 @@
         <v>456</v>
       </c>
       <c r="B490" s="7" t="s">
-        <v>1470</v>
+        <v>1467</v>
       </c>
       <c r="C490" s="7"/>
       <c r="D490" s="7"/>
       <c r="E490" s="9" t="s">
-        <v>1471</v>
+        <v>1468</v>
       </c>
       <c r="F490" s="7"/>
       <c r="G490" s="7"/>
@@ -19754,12 +19805,12 @@
         <v>456.1</v>
       </c>
       <c r="B491" s="7" t="s">
-        <v>1472</v>
+        <v>1469</v>
       </c>
       <c r="C491" s="7"/>
       <c r="D491" s="7"/>
       <c r="E491" s="9" t="s">
-        <v>1473</v>
+        <v>1470</v>
       </c>
       <c r="F491" s="7" t="s">
         <v>1081</v>
@@ -19778,12 +19829,12 @@
         <v>456.2</v>
       </c>
       <c r="B492" s="7" t="s">
-        <v>1474</v>
+        <v>1471</v>
       </c>
       <c r="C492" s="7"/>
       <c r="D492" s="7"/>
       <c r="E492" s="9" t="s">
-        <v>1475</v>
+        <v>1472</v>
       </c>
       <c r="F492" s="7" t="s">
         <v>1081</v>
@@ -19802,12 +19853,12 @@
         <v>456.3</v>
       </c>
       <c r="B493" s="7" t="s">
-        <v>1476</v>
+        <v>1473</v>
       </c>
       <c r="C493" s="7"/>
       <c r="D493" s="7"/>
       <c r="E493" s="9" t="s">
-        <v>1477</v>
+        <v>1474</v>
       </c>
       <c r="F493" s="7" t="s">
         <v>1081</v>
@@ -19826,12 +19877,12 @@
         <v>456.4</v>
       </c>
       <c r="B494" s="7" t="s">
-        <v>1478</v>
+        <v>1475</v>
       </c>
       <c r="C494" s="7"/>
       <c r="D494" s="7"/>
       <c r="E494" s="9" t="s">
-        <v>1479</v>
+        <v>1476</v>
       </c>
       <c r="F494" s="7" t="s">
         <v>1081</v>
@@ -19850,12 +19901,12 @@
         <v>456.5</v>
       </c>
       <c r="B495" s="7" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
       <c r="C495" s="7"/>
       <c r="D495" s="7"/>
       <c r="E495" s="9" t="s">
-        <v>1481</v>
+        <v>1478</v>
       </c>
       <c r="F495" s="7" t="s">
         <v>1081</v>
@@ -19874,7 +19925,7 @@
         <v>457</v>
       </c>
       <c r="B496" s="7" t="s">
-        <v>1482</v>
+        <v>1479</v>
       </c>
       <c r="C496" s="7"/>
       <c r="D496" s="7"/>
@@ -19896,7 +19947,7 @@
         <v>458</v>
       </c>
       <c r="B497" s="7" t="s">
-        <v>1483</v>
+        <v>1480</v>
       </c>
       <c r="C497" s="7"/>
       <c r="D497" s="7"/>
@@ -19920,7 +19971,7 @@
         <v>459</v>
       </c>
       <c r="B498" s="7" t="s">
-        <v>1484</v>
+        <v>1481</v>
       </c>
       <c r="C498" s="7"/>
       <c r="D498" s="7"/>
@@ -19942,12 +19993,12 @@
         <v>460</v>
       </c>
       <c r="B499" s="7" t="s">
-        <v>1485</v>
+        <v>1482</v>
       </c>
       <c r="C499" s="7"/>
       <c r="D499" s="7"/>
       <c r="E499" s="9" t="s">
-        <v>1486</v>
+        <v>1483</v>
       </c>
       <c r="F499" s="7" t="s">
         <v>610</v>
@@ -19966,12 +20017,12 @@
         <v>461</v>
       </c>
       <c r="B500" s="7" t="s">
-        <v>1487</v>
+        <v>1484</v>
       </c>
       <c r="C500" s="7"/>
       <c r="D500" s="7"/>
       <c r="E500" s="9" t="s">
-        <v>1488</v>
+        <v>1485</v>
       </c>
       <c r="F500" s="7" t="s">
         <v>610</v>
@@ -19990,12 +20041,12 @@
         <v>462</v>
       </c>
       <c r="B501" s="7" t="s">
-        <v>1489</v>
+        <v>1486</v>
       </c>
       <c r="C501" s="7"/>
       <c r="D501" s="7"/>
       <c r="E501" s="9" t="s">
-        <v>1490</v>
+        <v>1487</v>
       </c>
       <c r="F501" s="7" t="s">
         <v>610</v>
@@ -20014,7 +20065,7 @@
         <v>463</v>
       </c>
       <c r="B502" s="7" t="s">
-        <v>1491</v>
+        <v>1488</v>
       </c>
       <c r="C502" s="7"/>
       <c r="D502" s="7"/>
@@ -20036,7 +20087,7 @@
         <v>464</v>
       </c>
       <c r="B503" s="7" t="s">
-        <v>1492</v>
+        <v>1489</v>
       </c>
       <c r="C503" s="7"/>
       <c r="D503" s="7"/>
@@ -20058,12 +20109,12 @@
         <v>465</v>
       </c>
       <c r="B504" s="7" t="s">
-        <v>1493</v>
+        <v>1490</v>
       </c>
       <c r="C504" s="7"/>
       <c r="D504" s="7"/>
       <c r="E504" s="9" t="s">
-        <v>1494</v>
+        <v>1491</v>
       </c>
       <c r="F504" s="7" t="s">
         <v>610</v>
@@ -20072,7 +20123,7 @@
         <v>622</v>
       </c>
       <c r="H504" s="9" t="s">
-        <v>1495</v>
+        <v>1492</v>
       </c>
       <c r="I504" s="9" t="s">
         <v>1408</v>
@@ -20084,7 +20135,7 @@
         <v>466</v>
       </c>
       <c r="B505" s="7" t="s">
-        <v>1496</v>
+        <v>1493</v>
       </c>
       <c r="C505" s="7"/>
       <c r="D505" s="7"/>
@@ -20096,10 +20147,10 @@
         <v>618</v>
       </c>
       <c r="H505" s="9" t="s">
-        <v>1497</v>
+        <v>1494</v>
       </c>
       <c r="I505" s="9" t="s">
-        <v>1498</v>
+        <v>1495</v>
       </c>
       <c r="J505" s="9"/>
     </row>
@@ -20108,7 +20159,7 @@
         <v>467</v>
       </c>
       <c r="B506" s="7" t="s">
-        <v>1499</v>
+        <v>1496</v>
       </c>
       <c r="C506" s="7"/>
       <c r="D506" s="7"/>
@@ -20120,7 +20171,7 @@
         <v>618</v>
       </c>
       <c r="H506" s="9" t="s">
-        <v>1500</v>
+        <v>1497</v>
       </c>
       <c r="I506" s="9" t="s">
         <v>1408</v>
@@ -20132,7 +20183,7 @@
         <v>468</v>
       </c>
       <c r="B507" s="7" t="s">
-        <v>1501</v>
+        <v>1498</v>
       </c>
       <c r="C507" s="7"/>
       <c r="D507" s="7"/>
@@ -20154,7 +20205,7 @@
         <v>469</v>
       </c>
       <c r="B508" s="7" t="s">
-        <v>1502</v>
+        <v>1499</v>
       </c>
       <c r="C508" s="7"/>
       <c r="D508" s="7"/>
@@ -20166,7 +20217,7 @@
         <v>629</v>
       </c>
       <c r="H508" s="9" t="s">
-        <v>1503</v>
+        <v>1500</v>
       </c>
       <c r="I508" s="9" t="s">
         <v>1408</v>
@@ -20178,7 +20229,7 @@
         <v>470</v>
       </c>
       <c r="B509" s="7" t="s">
-        <v>1504</v>
+        <v>1501</v>
       </c>
       <c r="C509" s="7"/>
       <c r="D509" s="7"/>
@@ -20191,7 +20242,7 @@
       </c>
       <c r="H509" s="9"/>
       <c r="I509" s="9" t="s">
-        <v>1498</v>
+        <v>1495</v>
       </c>
       <c r="J509" s="9"/>
     </row>
@@ -20200,7 +20251,7 @@
         <v>471</v>
       </c>
       <c r="B510" s="7" t="s">
-        <v>1505</v>
+        <v>1502</v>
       </c>
       <c r="C510" s="7"/>
       <c r="D510" s="7"/>
@@ -20222,7 +20273,7 @@
         <v>472</v>
       </c>
       <c r="B511" s="7" t="s">
-        <v>1506</v>
+        <v>1503</v>
       </c>
       <c r="C511" s="7"/>
       <c r="D511" s="7"/>
@@ -20244,7 +20295,7 @@
         <v>473</v>
       </c>
       <c r="B512" s="7" t="s">
-        <v>1507</v>
+        <v>1504</v>
       </c>
       <c r="C512" s="7"/>
       <c r="D512" s="7"/>
@@ -20257,7 +20308,7 @@
       </c>
       <c r="H512" s="9"/>
       <c r="I512" s="9" t="s">
-        <v>1508</v>
+        <v>1505</v>
       </c>
       <c r="J512" s="9"/>
     </row>
@@ -20266,7 +20317,7 @@
         <v>474</v>
       </c>
       <c r="B513" s="7" t="s">
-        <v>1509</v>
+        <v>1506</v>
       </c>
       <c r="C513" s="7"/>
       <c r="D513" s="7"/>
@@ -20282,7 +20333,7 @@
         <v>1408</v>
       </c>
       <c r="J513" s="9" t="s">
-        <v>1510</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="514" s="2" customFormat="1" customHeight="1" spans="1:10">
@@ -20290,7 +20341,7 @@
         <v>475</v>
       </c>
       <c r="B514" s="7" t="s">
-        <v>1511</v>
+        <v>1508</v>
       </c>
       <c r="C514" s="7"/>
       <c r="D514" s="7"/>
@@ -20312,19 +20363,19 @@
         <v>476</v>
       </c>
       <c r="B515" s="7" t="s">
-        <v>1512</v>
+        <v>1509</v>
       </c>
       <c r="C515" s="7"/>
       <c r="D515" s="7"/>
       <c r="E515" s="9" t="s">
-        <v>1513</v>
+        <v>1510</v>
       </c>
       <c r="F515" s="7"/>
       <c r="G515" s="7" t="s">
         <v>622</v>
       </c>
       <c r="H515" s="9" t="s">
-        <v>1514</v>
+        <v>1511</v>
       </c>
       <c r="I515" s="9" t="s">
         <v>1408</v>
@@ -20336,12 +20387,12 @@
         <v>477</v>
       </c>
       <c r="B516" s="7" t="s">
-        <v>1515</v>
+        <v>1512</v>
       </c>
       <c r="C516" s="7"/>
       <c r="D516" s="7"/>
       <c r="E516" s="9" t="s">
-        <v>1513</v>
+        <v>1510</v>
       </c>
       <c r="F516" s="7"/>
       <c r="G516" s="7" t="s">
@@ -20358,12 +20409,12 @@
         <v>478</v>
       </c>
       <c r="B517" s="7" t="s">
-        <v>1516</v>
+        <v>1513</v>
       </c>
       <c r="C517" s="7"/>
       <c r="D517" s="7"/>
       <c r="E517" s="9" t="s">
-        <v>1513</v>
+        <v>1510</v>
       </c>
       <c r="F517" s="7"/>
       <c r="G517" s="7" t="s">
@@ -20380,19 +20431,19 @@
         <v>479</v>
       </c>
       <c r="B518" s="7" t="s">
-        <v>1517</v>
+        <v>1514</v>
       </c>
       <c r="C518" s="7"/>
       <c r="D518" s="7"/>
       <c r="E518" s="9" t="s">
-        <v>1513</v>
+        <v>1510</v>
       </c>
       <c r="F518" s="7"/>
       <c r="G518" s="7" t="s">
         <v>1058</v>
       </c>
       <c r="H518" s="9" t="s">
-        <v>1518</v>
+        <v>1515</v>
       </c>
       <c r="I518" s="9" t="s">
         <v>1408</v>
@@ -20404,12 +20455,12 @@
         <v>480</v>
       </c>
       <c r="B519" s="7" t="s">
-        <v>1519</v>
+        <v>1516</v>
       </c>
       <c r="C519" s="7"/>
       <c r="D519" s="7"/>
       <c r="E519" s="9" t="s">
-        <v>1520</v>
+        <v>1517</v>
       </c>
       <c r="F519" s="7"/>
       <c r="G519" s="7" t="s">
@@ -20426,13 +20477,13 @@
         <v>481</v>
       </c>
       <c r="B520" s="7" t="s">
-        <v>1521</v>
+        <v>1518</v>
       </c>
       <c r="C520" s="7"/>
       <c r="D520" s="7"/>
       <c r="E520" s="9"/>
       <c r="F520" s="7" t="s">
-        <v>1522</v>
+        <v>1519</v>
       </c>
       <c r="G520" s="7" t="s">
         <v>622</v>
@@ -20448,12 +20499,12 @@
         <v>482</v>
       </c>
       <c r="B521" s="7" t="s">
-        <v>1523</v>
+        <v>1520</v>
       </c>
       <c r="C521" s="7"/>
       <c r="D521" s="7"/>
       <c r="E521" s="9" t="s">
-        <v>1524</v>
+        <v>1521</v>
       </c>
       <c r="F521" s="7"/>
       <c r="G521" s="7"/>
@@ -20468,25 +20519,25 @@
         <v>482.1</v>
       </c>
       <c r="B522" s="7" t="s">
-        <v>1525</v>
+        <v>1522</v>
       </c>
       <c r="C522" s="7"/>
       <c r="D522" s="7"/>
       <c r="E522" s="9" t="s">
-        <v>1526</v>
+        <v>1523</v>
       </c>
       <c r="F522" s="7"/>
       <c r="G522" s="7" t="s">
         <v>717</v>
       </c>
       <c r="H522" s="9" t="s">
-        <v>1527</v>
+        <v>1524</v>
       </c>
       <c r="I522" s="9" t="s">
         <v>1408</v>
       </c>
       <c r="J522" s="9" t="s">
-        <v>1528</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="523" s="2" customFormat="1" customHeight="1" spans="1:10">
@@ -20494,25 +20545,25 @@
         <v>482.2</v>
       </c>
       <c r="B523" s="7" t="s">
-        <v>1529</v>
+        <v>1526</v>
       </c>
       <c r="C523" s="7"/>
       <c r="D523" s="7"/>
       <c r="E523" s="9" t="s">
-        <v>1530</v>
+        <v>1527</v>
       </c>
       <c r="F523" s="7"/>
       <c r="G523" s="7" t="s">
         <v>611</v>
       </c>
       <c r="H523" s="9" t="s">
-        <v>1531</v>
+        <v>1528</v>
       </c>
       <c r="I523" s="9" t="s">
         <v>1408</v>
       </c>
       <c r="J523" s="9" t="s">
-        <v>1532</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="524" s="2" customFormat="1" customHeight="1" spans="1:10">
@@ -20520,23 +20571,23 @@
         <v>482.3</v>
       </c>
       <c r="B524" s="7" t="s">
-        <v>1533</v>
+        <v>1530</v>
       </c>
       <c r="C524" s="7"/>
       <c r="D524" s="7"/>
       <c r="E524" s="9" t="s">
-        <v>1534</v>
+        <v>1531</v>
       </c>
       <c r="F524" s="7"/>
       <c r="G524" s="7" t="s">
         <v>1411</v>
       </c>
       <c r="H524" s="9" t="s">
-        <v>1535</v>
+        <v>1532</v>
       </c>
       <c r="I524" s="9"/>
       <c r="J524" s="9" t="s">
-        <v>1536</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="525" s="2" customFormat="1" customHeight="1" spans="1:10">
@@ -20544,25 +20595,25 @@
         <v>482.4</v>
       </c>
       <c r="B525" s="7" t="s">
-        <v>1537</v>
+        <v>1534</v>
       </c>
       <c r="C525" s="7"/>
       <c r="D525" s="7"/>
       <c r="E525" s="9" t="s">
-        <v>1538</v>
+        <v>1535</v>
       </c>
       <c r="F525" s="7"/>
       <c r="G525" s="7" t="s">
         <v>622</v>
       </c>
       <c r="H525" s="9" t="s">
-        <v>1539</v>
+        <v>1536</v>
       </c>
       <c r="I525" s="9" t="s">
         <v>1408</v>
       </c>
       <c r="J525" s="9" t="s">
-        <v>1540</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="526" s="2" customFormat="1" customHeight="1" spans="1:10">
@@ -20570,23 +20621,23 @@
         <v>482.5</v>
       </c>
       <c r="B526" s="7" t="s">
-        <v>1541</v>
+        <v>1538</v>
       </c>
       <c r="C526" s="7"/>
       <c r="D526" s="7"/>
       <c r="E526" s="9" t="s">
-        <v>1542</v>
+        <v>1539</v>
       </c>
       <c r="F526" s="7"/>
       <c r="G526" s="7" t="s">
         <v>641</v>
       </c>
       <c r="H526" s="9" t="s">
-        <v>1543</v>
+        <v>1540</v>
       </c>
       <c r="I526" s="9"/>
       <c r="J526" s="9" t="s">
-        <v>1540</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="527" s="2" customFormat="1" customHeight="1" spans="1:10">
@@ -20594,19 +20645,19 @@
         <v>483</v>
       </c>
       <c r="B527" s="7" t="s">
-        <v>1544</v>
+        <v>1541</v>
       </c>
       <c r="C527" s="7"/>
       <c r="D527" s="7"/>
       <c r="E527" s="9"/>
       <c r="F527" s="7" t="s">
-        <v>1522</v>
+        <v>1519</v>
       </c>
       <c r="G527" s="7" t="s">
         <v>618</v>
       </c>
       <c r="H527" s="9" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="I527" s="9" t="s">
         <v>1408</v>
@@ -20618,19 +20669,19 @@
         <v>484</v>
       </c>
       <c r="B528" s="7" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="C528" s="7"/>
       <c r="D528" s="7"/>
       <c r="E528" s="9" t="s">
-        <v>1547</v>
+        <v>1544</v>
       </c>
       <c r="F528" s="7"/>
       <c r="G528" s="7" t="s">
         <v>717</v>
       </c>
       <c r="H528" s="9" t="s">
-        <v>1548</v>
+        <v>1545</v>
       </c>
       <c r="I528" s="9" t="s">
         <v>1408</v>
@@ -20642,12 +20693,12 @@
         <v>485</v>
       </c>
       <c r="B529" s="7" t="s">
-        <v>1549</v>
+        <v>1546</v>
       </c>
       <c r="C529" s="7"/>
       <c r="D529" s="7"/>
       <c r="E529" s="9" t="s">
-        <v>1550</v>
+        <v>1547</v>
       </c>
       <c r="F529" s="7"/>
       <c r="G529" s="7" t="s">
@@ -20655,7 +20706,7 @@
       </c>
       <c r="H529" s="9"/>
       <c r="I529" s="9" t="s">
-        <v>1498</v>
+        <v>1495</v>
       </c>
       <c r="J529" s="9"/>
     </row>
@@ -20664,12 +20715,12 @@
         <v>486</v>
       </c>
       <c r="B530" s="7" t="s">
-        <v>1551</v>
+        <v>1548</v>
       </c>
       <c r="C530" s="7"/>
       <c r="D530" s="7"/>
       <c r="E530" s="9" t="s">
-        <v>1550</v>
+        <v>1547</v>
       </c>
       <c r="F530" s="7"/>
       <c r="G530" s="7" t="s">
@@ -20686,7 +20737,7 @@
         <v>487</v>
       </c>
       <c r="B531" s="7" t="s">
-        <v>1552</v>
+        <v>1549</v>
       </c>
       <c r="C531" s="7"/>
       <c r="D531" s="7"/>
@@ -20698,7 +20749,7 @@
         <v>641</v>
       </c>
       <c r="H531" s="9" t="s">
-        <v>1553</v>
+        <v>1550</v>
       </c>
       <c r="I531" s="9" t="s">
         <v>1408</v>
@@ -20710,19 +20761,19 @@
         <v>488</v>
       </c>
       <c r="B532" s="7" t="s">
-        <v>1554</v>
+        <v>1551</v>
       </c>
       <c r="C532" s="7"/>
       <c r="D532" s="7"/>
       <c r="E532" s="9" t="s">
-        <v>1555</v>
+        <v>1552</v>
       </c>
       <c r="F532" s="7"/>
       <c r="G532" s="7" t="s">
         <v>622</v>
       </c>
       <c r="H532" s="9" t="s">
-        <v>1556</v>
+        <v>1553</v>
       </c>
       <c r="I532" s="9" t="s">
         <v>1408</v>
@@ -20734,12 +20785,12 @@
         <v>489</v>
       </c>
       <c r="B533" s="7" t="s">
-        <v>1557</v>
+        <v>1554</v>
       </c>
       <c r="C533" s="7"/>
       <c r="D533" s="7"/>
       <c r="E533" s="9" t="s">
-        <v>1558</v>
+        <v>1555</v>
       </c>
       <c r="F533" s="7"/>
       <c r="G533" s="7" t="s">
@@ -20756,13 +20807,13 @@
         <v>490</v>
       </c>
       <c r="B534" s="7" t="s">
-        <v>1559</v>
+        <v>1556</v>
       </c>
       <c r="C534" s="7"/>
       <c r="D534" s="7"/>
       <c r="E534" s="9"/>
       <c r="F534" s="7" t="s">
-        <v>1560</v>
+        <v>1557</v>
       </c>
       <c r="G534" s="7" t="s">
         <v>717</v>
@@ -20778,12 +20829,12 @@
         <v>491</v>
       </c>
       <c r="B535" s="7" t="s">
-        <v>1561</v>
+        <v>1558</v>
       </c>
       <c r="C535" s="7"/>
       <c r="D535" s="7"/>
       <c r="E535" s="9" t="s">
-        <v>1562</v>
+        <v>1559</v>
       </c>
       <c r="F535" s="7"/>
       <c r="G535" s="7" t="s">
@@ -20800,7 +20851,7 @@
         <v>492</v>
       </c>
       <c r="B536" s="7" t="s">
-        <v>1563</v>
+        <v>1560</v>
       </c>
       <c r="C536" s="7"/>
       <c r="D536" s="7"/>
@@ -20822,7 +20873,7 @@
         <v>493</v>
       </c>
       <c r="B537" s="7" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="C537" s="7"/>
       <c r="D537" s="7"/>
@@ -20834,13 +20885,13 @@
         <v>618</v>
       </c>
       <c r="H537" s="9" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="I537" s="9" t="s">
         <v>1408</v>
       </c>
       <c r="J537" s="9" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="538" s="2" customFormat="1" customHeight="1" spans="1:10">
@@ -20848,12 +20899,12 @@
         <v>494</v>
       </c>
       <c r="B538" s="7" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="C538" s="7"/>
       <c r="D538" s="7"/>
       <c r="E538" s="9" t="s">
-        <v>1568</v>
+        <v>1565</v>
       </c>
       <c r="F538" s="7"/>
       <c r="G538" s="7" t="s">
@@ -20870,19 +20921,19 @@
         <v>495</v>
       </c>
       <c r="B539" s="7" t="s">
-        <v>1569</v>
+        <v>1566</v>
       </c>
       <c r="C539" s="7"/>
       <c r="D539" s="7"/>
       <c r="E539" s="9" t="s">
-        <v>1570</v>
+        <v>1567</v>
       </c>
       <c r="F539" s="7"/>
       <c r="G539" s="7" t="s">
         <v>635</v>
       </c>
       <c r="H539" s="9" t="s">
-        <v>1571</v>
+        <v>1568</v>
       </c>
       <c r="I539" s="9" t="s">
         <v>1408</v>
@@ -20894,12 +20945,12 @@
         <v>496</v>
       </c>
       <c r="B540" s="7" t="s">
-        <v>1572</v>
+        <v>1569</v>
       </c>
       <c r="C540" s="7"/>
       <c r="D540" s="7"/>
       <c r="E540" s="9" t="s">
-        <v>1573</v>
+        <v>1570</v>
       </c>
       <c r="F540" s="7"/>
       <c r="G540" s="7" t="s">
@@ -20916,7 +20967,7 @@
         <v>497</v>
       </c>
       <c r="B541" s="7" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="C541" s="7"/>
       <c r="D541" s="7"/>
@@ -20928,13 +20979,13 @@
         <v>717</v>
       </c>
       <c r="H541" s="9" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="I541" s="9" t="s">
         <v>1408</v>
       </c>
       <c r="J541" s="9" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="542" s="2" customFormat="1" customHeight="1" spans="1:10">
@@ -20942,7 +20993,7 @@
         <v>498</v>
       </c>
       <c r="B542" s="7" t="s">
-        <v>1577</v>
+        <v>1574</v>
       </c>
       <c r="C542" s="7"/>
       <c r="D542" s="7"/>
@@ -20964,7 +21015,7 @@
         <v>499</v>
       </c>
       <c r="B543" s="7" t="s">
-        <v>1578</v>
+        <v>1575</v>
       </c>
       <c r="C543" s="7"/>
       <c r="D543" s="7"/>
@@ -20976,13 +21027,13 @@
         <v>668</v>
       </c>
       <c r="H543" s="9" t="s">
-        <v>1579</v>
+        <v>1576</v>
       </c>
       <c r="I543" s="9" t="s">
         <v>1408</v>
       </c>
       <c r="J543" s="9" t="s">
-        <v>1580</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="544" s="2" customFormat="1" customHeight="1" spans="1:10">
@@ -20990,7 +21041,7 @@
         <v>500</v>
       </c>
       <c r="B544" s="7" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="C544" s="7"/>
       <c r="D544" s="7"/>
@@ -21012,7 +21063,7 @@
         <v>501</v>
       </c>
       <c r="B545" s="7" t="s">
-        <v>1582</v>
+        <v>1579</v>
       </c>
       <c r="C545" s="7"/>
       <c r="D545" s="7"/>
@@ -21034,7 +21085,7 @@
         <v>502</v>
       </c>
       <c r="B546" s="7" t="s">
-        <v>1583</v>
+        <v>1580</v>
       </c>
       <c r="C546" s="7"/>
       <c r="D546" s="7"/>
@@ -21046,7 +21097,7 @@
         <v>676</v>
       </c>
       <c r="H546" s="9" t="s">
-        <v>1584</v>
+        <v>1581</v>
       </c>
       <c r="I546" s="9" t="s">
         <v>1408</v>
@@ -21060,7 +21111,7 @@
         <v>503</v>
       </c>
       <c r="B547" s="7" t="s">
-        <v>1585</v>
+        <v>1582</v>
       </c>
       <c r="C547" s="7"/>
       <c r="D547" s="7"/>
@@ -21072,7 +21123,7 @@
         <v>676</v>
       </c>
       <c r="H547" s="9" t="s">
-        <v>1586</v>
+        <v>1583</v>
       </c>
       <c r="I547" s="9" t="s">
         <v>1408</v>
@@ -21084,7 +21135,7 @@
         <v>504</v>
       </c>
       <c r="B548" s="7" t="s">
-        <v>1587</v>
+        <v>1584</v>
       </c>
       <c r="C548" s="7"/>
       <c r="D548" s="7"/>
@@ -21096,13 +21147,13 @@
         <v>676</v>
       </c>
       <c r="H548" s="9" t="s">
-        <v>1588</v>
+        <v>1585</v>
       </c>
       <c r="I548" s="9" t="s">
         <v>1408</v>
       </c>
       <c r="J548" s="9" t="s">
-        <v>1536</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="549" s="2" customFormat="1" customHeight="1" spans="1:10">
@@ -21110,7 +21161,7 @@
         <v>505</v>
       </c>
       <c r="B549" s="7" t="s">
-        <v>1589</v>
+        <v>1586</v>
       </c>
       <c r="C549" s="7"/>
       <c r="D549" s="7"/>
@@ -21132,7 +21183,7 @@
         <v>506</v>
       </c>
       <c r="B550" s="7" t="s">
-        <v>1590</v>
+        <v>1587</v>
       </c>
       <c r="C550" s="7"/>
       <c r="D550" s="7"/>
@@ -21144,7 +21195,7 @@
         <v>676</v>
       </c>
       <c r="H550" s="9" t="s">
-        <v>1591</v>
+        <v>1588</v>
       </c>
       <c r="I550" s="9" t="s">
         <v>1408</v>
@@ -21156,7 +21207,7 @@
         <v>507</v>
       </c>
       <c r="B551" s="7" t="s">
-        <v>1592</v>
+        <v>1589</v>
       </c>
       <c r="C551" s="7"/>
       <c r="D551" s="7"/>
@@ -21168,13 +21219,13 @@
         <v>635</v>
       </c>
       <c r="H551" s="9" t="s">
-        <v>1593</v>
+        <v>1590</v>
       </c>
       <c r="I551" s="9" t="s">
         <v>1408</v>
       </c>
       <c r="J551" s="9" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="552" s="2" customFormat="1" customHeight="1" spans="1:10">
@@ -21182,7 +21233,7 @@
         <v>508</v>
       </c>
       <c r="B552" s="7" t="s">
-        <v>1594</v>
+        <v>1591</v>
       </c>
       <c r="C552" s="7"/>
       <c r="D552" s="7"/>
@@ -21191,16 +21242,16 @@
         <v>1376</v>
       </c>
       <c r="G552" s="7" t="s">
-        <v>1595</v>
+        <v>1592</v>
       </c>
       <c r="H552" s="9" t="s">
-        <v>1596</v>
+        <v>1593</v>
       </c>
       <c r="I552" s="9" t="s">
         <v>1408</v>
       </c>
       <c r="J552" s="9" t="s">
-        <v>1597</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="553" s="2" customFormat="1" customHeight="1" spans="1:10">
@@ -21208,7 +21259,7 @@
         <v>509</v>
       </c>
       <c r="B553" s="7" t="s">
-        <v>1598</v>
+        <v>1595</v>
       </c>
       <c r="C553" s="7"/>
       <c r="D553" s="7"/>
@@ -21230,7 +21281,7 @@
         <v>510</v>
       </c>
       <c r="B554" s="7" t="s">
-        <v>1599</v>
+        <v>1596</v>
       </c>
       <c r="C554" s="7"/>
       <c r="D554" s="7"/>
@@ -21242,13 +21293,13 @@
         <v>622</v>
       </c>
       <c r="H554" s="9" t="s">
-        <v>1600</v>
+        <v>1597</v>
       </c>
       <c r="I554" s="9" t="s">
         <v>1408</v>
       </c>
       <c r="J554" s="9" t="s">
-        <v>1532</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="555" s="2" customFormat="1" customHeight="1" spans="1:10">
@@ -21256,7 +21307,7 @@
         <v>511</v>
       </c>
       <c r="B555" s="7" t="s">
-        <v>1601</v>
+        <v>1598</v>
       </c>
       <c r="C555" s="7"/>
       <c r="D555" s="7"/>
@@ -21268,7 +21319,7 @@
         <v>622</v>
       </c>
       <c r="H555" s="9" t="s">
-        <v>1602</v>
+        <v>1599</v>
       </c>
       <c r="I555" s="9" t="s">
         <v>1408</v>
@@ -21280,7 +21331,7 @@
         <v>512</v>
       </c>
       <c r="B556" s="7" t="s">
-        <v>1603</v>
+        <v>1600</v>
       </c>
       <c r="C556" s="7"/>
       <c r="D556" s="7"/>
@@ -21292,13 +21343,13 @@
         <v>622</v>
       </c>
       <c r="H556" s="9" t="s">
-        <v>1604</v>
+        <v>1601</v>
       </c>
       <c r="I556" s="9" t="s">
         <v>1408</v>
       </c>
       <c r="J556" s="9" t="s">
-        <v>1605</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="557" s="2" customFormat="1" customHeight="1" spans="1:10">
@@ -21306,7 +21357,7 @@
         <v>513</v>
       </c>
       <c r="B557" s="7" t="s">
-        <v>1606</v>
+        <v>1603</v>
       </c>
       <c r="C557" s="7"/>
       <c r="D557" s="7"/>
@@ -21315,7 +21366,7 @@
         <v>1376</v>
       </c>
       <c r="G557" s="7" t="s">
-        <v>1607</v>
+        <v>1604</v>
       </c>
       <c r="H557" s="9"/>
       <c r="I557" s="9" t="s">
@@ -21328,7 +21379,7 @@
         <v>514</v>
       </c>
       <c r="B558" s="7" t="s">
-        <v>1608</v>
+        <v>1605</v>
       </c>
       <c r="C558" s="7"/>
       <c r="D558" s="7"/>
@@ -21337,7 +21388,7 @@
         <v>1376</v>
       </c>
       <c r="G558" s="7" t="s">
-        <v>1607</v>
+        <v>1604</v>
       </c>
       <c r="H558" s="9"/>
       <c r="I558" s="9" t="s">
@@ -21350,7 +21401,7 @@
         <v>515</v>
       </c>
       <c r="B559" s="7" t="s">
-        <v>1609</v>
+        <v>1606</v>
       </c>
       <c r="C559" s="7"/>
       <c r="D559" s="7"/>
@@ -21359,7 +21410,7 @@
         <v>1376</v>
       </c>
       <c r="G559" s="7" t="s">
-        <v>1607</v>
+        <v>1604</v>
       </c>
       <c r="H559" s="9"/>
       <c r="I559" s="9" t="s">
@@ -21372,7 +21423,7 @@
         <v>516</v>
       </c>
       <c r="B560" s="7" t="s">
-        <v>1610</v>
+        <v>1607</v>
       </c>
       <c r="C560" s="7"/>
       <c r="D560" s="7"/>
@@ -21396,7 +21447,7 @@
         <v>517</v>
       </c>
       <c r="B561" s="7" t="s">
-        <v>1611</v>
+        <v>1608</v>
       </c>
       <c r="C561" s="7"/>
       <c r="D561" s="7"/>
@@ -21418,7 +21469,7 @@
         <v>518</v>
       </c>
       <c r="B562" s="7" t="s">
-        <v>1612</v>
+        <v>1609</v>
       </c>
       <c r="C562" s="7"/>
       <c r="D562" s="7"/>
@@ -21440,7 +21491,7 @@
         <v>519</v>
       </c>
       <c r="B563" s="7" t="s">
-        <v>1613</v>
+        <v>1610</v>
       </c>
       <c r="C563" s="7"/>
       <c r="D563" s="7"/>
@@ -21462,7 +21513,7 @@
         <v>520</v>
       </c>
       <c r="B564" s="7" t="s">
-        <v>1614</v>
+        <v>1611</v>
       </c>
       <c r="C564" s="7"/>
       <c r="D564" s="7"/>
@@ -21484,7 +21535,7 @@
         <v>521</v>
       </c>
       <c r="B565" s="7" t="s">
-        <v>1615</v>
+        <v>1612</v>
       </c>
       <c r="C565" s="7"/>
       <c r="D565" s="7"/>
@@ -21506,7 +21557,7 @@
         <v>522</v>
       </c>
       <c r="B566" s="7" t="s">
-        <v>1616</v>
+        <v>1613</v>
       </c>
       <c r="C566" s="7"/>
       <c r="D566" s="7"/>
@@ -21528,7 +21579,7 @@
         <v>523</v>
       </c>
       <c r="B567" s="7" t="s">
-        <v>1617</v>
+        <v>1614</v>
       </c>
       <c r="C567" s="7"/>
       <c r="D567" s="7"/>
@@ -21540,7 +21591,7 @@
         <v>641</v>
       </c>
       <c r="H567" s="9" t="s">
-        <v>1618</v>
+        <v>1615</v>
       </c>
       <c r="I567" s="9" t="s">
         <v>1408</v>
@@ -21552,7 +21603,7 @@
         <v>524</v>
       </c>
       <c r="B568" s="7" t="s">
-        <v>1619</v>
+        <v>1616</v>
       </c>
       <c r="C568" s="7"/>
       <c r="D568" s="7"/>
@@ -21574,7 +21625,7 @@
         <v>525</v>
       </c>
       <c r="B569" s="7" t="s">
-        <v>1620</v>
+        <v>1617</v>
       </c>
       <c r="C569" s="7"/>
       <c r="D569" s="7"/>
@@ -21596,7 +21647,7 @@
         <v>526</v>
       </c>
       <c r="B570" s="7" t="s">
-        <v>1621</v>
+        <v>1618</v>
       </c>
       <c r="C570" s="7"/>
       <c r="D570" s="7"/>
@@ -21618,7 +21669,7 @@
         <v>527</v>
       </c>
       <c r="B571" s="7" t="s">
-        <v>1622</v>
+        <v>1619</v>
       </c>
       <c r="C571" s="7"/>
       <c r="D571" s="7"/>
@@ -21640,7 +21691,7 @@
         <v>528</v>
       </c>
       <c r="B572" s="7" t="s">
-        <v>1623</v>
+        <v>1620</v>
       </c>
       <c r="C572" s="7"/>
       <c r="D572" s="7"/>
@@ -21662,7 +21713,7 @@
         <v>529</v>
       </c>
       <c r="B573" s="7" t="s">
-        <v>1624</v>
+        <v>1621</v>
       </c>
       <c r="C573" s="7"/>
       <c r="D573" s="7"/>
@@ -21684,7 +21735,7 @@
         <v>530</v>
       </c>
       <c r="B574" s="7" t="s">
-        <v>1625</v>
+        <v>1622</v>
       </c>
       <c r="C574" s="7"/>
       <c r="D574" s="7"/>
@@ -21696,7 +21747,7 @@
         <v>641</v>
       </c>
       <c r="H574" s="9" t="s">
-        <v>1626</v>
+        <v>1623</v>
       </c>
       <c r="I574" s="9" t="s">
         <v>1408</v>
@@ -21708,7 +21759,7 @@
         <v>531</v>
       </c>
       <c r="B575" s="7" t="s">
-        <v>1627</v>
+        <v>1624</v>
       </c>
       <c r="C575" s="7"/>
       <c r="D575" s="7"/>
@@ -21730,7 +21781,7 @@
         <v>532</v>
       </c>
       <c r="B576" s="7" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
       <c r="C576" s="7"/>
       <c r="D576" s="7"/>
@@ -21742,7 +21793,7 @@
         <v>618</v>
       </c>
       <c r="H576" s="9" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
       <c r="I576" s="9" t="s">
         <v>1408</v>
@@ -21754,7 +21805,7 @@
         <v>533</v>
       </c>
       <c r="B577" s="7" t="s">
-        <v>1630</v>
+        <v>1627</v>
       </c>
       <c r="C577" s="7"/>
       <c r="D577" s="7"/>
@@ -21766,7 +21817,7 @@
         <v>618</v>
       </c>
       <c r="H577" s="9" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
       <c r="I577" s="9" t="s">
         <v>1408</v>
@@ -21778,7 +21829,7 @@
         <v>534</v>
       </c>
       <c r="B578" s="7" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
       <c r="C578" s="7"/>
       <c r="D578" s="7"/>
@@ -21794,7 +21845,7 @@
         <v>1408</v>
       </c>
       <c r="J578" s="9" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="579" s="2" customFormat="1" customHeight="1" spans="1:10">
@@ -21802,7 +21853,7 @@
         <v>535</v>
       </c>
       <c r="B579" s="7" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
       <c r="C579" s="7"/>
       <c r="D579" s="7"/>
@@ -21814,13 +21865,13 @@
         <v>618</v>
       </c>
       <c r="H579" s="9" t="s">
-        <v>1634</v>
+        <v>1631</v>
       </c>
       <c r="I579" s="9" t="s">
         <v>1408</v>
       </c>
       <c r="J579" s="9" t="s">
-        <v>1635</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="580" s="2" customFormat="1" customHeight="1" spans="1:10">
@@ -21828,7 +21879,7 @@
         <v>536</v>
       </c>
       <c r="B580" s="7" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
       <c r="C580" s="7"/>
       <c r="D580" s="7"/>
@@ -21850,7 +21901,7 @@
         <v>537</v>
       </c>
       <c r="B581" s="7" t="s">
-        <v>1637</v>
+        <v>1634</v>
       </c>
       <c r="C581" s="7"/>
       <c r="D581" s="7"/>
@@ -21866,7 +21917,7 @@
         <v>1408</v>
       </c>
       <c r="J581" s="9" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="582" s="2" customFormat="1" customHeight="1" spans="1:10">
@@ -21874,7 +21925,7 @@
         <v>538</v>
       </c>
       <c r="B582" s="7" t="s">
-        <v>1638</v>
+        <v>1635</v>
       </c>
       <c r="C582" s="7"/>
       <c r="D582" s="7"/>
@@ -21886,13 +21937,13 @@
         <v>618</v>
       </c>
       <c r="H582" s="9" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
       <c r="I582" s="9" t="s">
         <v>1408</v>
       </c>
       <c r="J582" s="9" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="583" s="2" customFormat="1" customHeight="1" spans="1:10">
@@ -21900,7 +21951,7 @@
         <v>539</v>
       </c>
       <c r="B583" s="7" t="s">
-        <v>1640</v>
+        <v>1637</v>
       </c>
       <c r="C583" s="7"/>
       <c r="D583" s="7"/>
@@ -21912,13 +21963,13 @@
         <v>618</v>
       </c>
       <c r="H583" s="9" t="s">
-        <v>1641</v>
+        <v>1638</v>
       </c>
       <c r="I583" s="9" t="s">
         <v>1408</v>
       </c>
       <c r="J583" s="9" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="584" s="2" customFormat="1" customHeight="1" spans="1:10">
@@ -21926,7 +21977,7 @@
         <v>540</v>
       </c>
       <c r="B584" s="7" t="s">
-        <v>1642</v>
+        <v>1639</v>
       </c>
       <c r="C584" s="7"/>
       <c r="D584" s="7"/>
@@ -21938,13 +21989,13 @@
         <v>618</v>
       </c>
       <c r="H584" s="9" t="s">
-        <v>1643</v>
+        <v>1640</v>
       </c>
       <c r="I584" s="9" t="s">
         <v>1408</v>
       </c>
       <c r="J584" s="9" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="585" s="2" customFormat="1" customHeight="1" spans="1:10">
@@ -21952,7 +22003,7 @@
         <v>541</v>
       </c>
       <c r="B585" s="7" t="s">
-        <v>1644</v>
+        <v>1641</v>
       </c>
       <c r="C585" s="7"/>
       <c r="D585" s="7"/>
@@ -21974,7 +22025,7 @@
         <v>542</v>
       </c>
       <c r="B586" s="7" t="s">
-        <v>1645</v>
+        <v>1642</v>
       </c>
       <c r="C586" s="7"/>
       <c r="D586" s="7"/>
@@ -21996,7 +22047,7 @@
         <v>543</v>
       </c>
       <c r="B587" s="7" t="s">
-        <v>1646</v>
+        <v>1643</v>
       </c>
       <c r="C587" s="7"/>
       <c r="D587" s="7"/>
@@ -22008,7 +22059,7 @@
         <v>618</v>
       </c>
       <c r="H587" s="9" t="s">
-        <v>1647</v>
+        <v>1644</v>
       </c>
       <c r="I587" s="9" t="s">
         <v>1408</v>
@@ -22020,7 +22071,7 @@
         <v>544</v>
       </c>
       <c r="B588" s="7" t="s">
-        <v>1648</v>
+        <v>1645</v>
       </c>
       <c r="C588" s="7"/>
       <c r="D588" s="7"/>
@@ -22042,7 +22093,7 @@
         <v>545</v>
       </c>
       <c r="B589" s="7" t="s">
-        <v>1649</v>
+        <v>1646</v>
       </c>
       <c r="C589" s="7"/>
       <c r="D589" s="7"/>
@@ -22054,7 +22105,7 @@
         <v>638</v>
       </c>
       <c r="H589" s="9" t="s">
-        <v>1650</v>
+        <v>1647</v>
       </c>
       <c r="I589" s="9" t="s">
         <v>1408</v>
@@ -22066,7 +22117,7 @@
         <v>546</v>
       </c>
       <c r="B590" s="7" t="s">
-        <v>1651</v>
+        <v>1648</v>
       </c>
       <c r="C590" s="7"/>
       <c r="D590" s="7"/>
@@ -22078,7 +22129,7 @@
         <v>638</v>
       </c>
       <c r="H590" s="9" t="s">
-        <v>1652</v>
+        <v>1649</v>
       </c>
       <c r="I590" s="9" t="s">
         <v>1408</v>
@@ -22090,7 +22141,7 @@
         <v>547</v>
       </c>
       <c r="B591" s="7" t="s">
-        <v>1653</v>
+        <v>1650</v>
       </c>
       <c r="C591" s="7"/>
       <c r="D591" s="7"/>
@@ -22102,7 +22153,7 @@
         <v>626</v>
       </c>
       <c r="H591" s="9" t="s">
-        <v>1654</v>
+        <v>1651</v>
       </c>
       <c r="I591" s="9" t="s">
         <v>1408</v>
@@ -22114,7 +22165,7 @@
         <v>548</v>
       </c>
       <c r="B592" s="7" t="s">
-        <v>1655</v>
+        <v>1652</v>
       </c>
       <c r="C592" s="7"/>
       <c r="D592" s="7"/>
@@ -22136,7 +22187,7 @@
         <v>549</v>
       </c>
       <c r="B593" s="7" t="s">
-        <v>1656</v>
+        <v>1653</v>
       </c>
       <c r="C593" s="7"/>
       <c r="D593" s="7"/>
@@ -22158,7 +22209,7 @@
         <v>550</v>
       </c>
       <c r="B594" s="7" t="s">
-        <v>1657</v>
+        <v>1654</v>
       </c>
       <c r="C594" s="7"/>
       <c r="D594" s="7"/>
@@ -22170,7 +22221,7 @@
         <v>629</v>
       </c>
       <c r="H594" s="9" t="s">
-        <v>1658</v>
+        <v>1655</v>
       </c>
       <c r="I594" s="9" t="s">
         <v>1408</v>
@@ -22184,7 +22235,7 @@
         <v>551</v>
       </c>
       <c r="B595" s="7" t="s">
-        <v>1659</v>
+        <v>1656</v>
       </c>
       <c r="C595" s="7"/>
       <c r="D595" s="7"/>
@@ -22206,7 +22257,7 @@
         <v>552</v>
       </c>
       <c r="B596" s="7" t="s">
-        <v>1660</v>
+        <v>1657</v>
       </c>
       <c r="C596" s="7"/>
       <c r="D596" s="7"/>
@@ -22228,7 +22279,7 @@
         <v>553</v>
       </c>
       <c r="B597" s="7" t="s">
-        <v>1661</v>
+        <v>1658</v>
       </c>
       <c r="C597" s="7"/>
       <c r="D597" s="7"/>
@@ -22250,7 +22301,7 @@
         <v>554</v>
       </c>
       <c r="B598" s="7" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
       <c r="C598" s="7"/>
       <c r="D598" s="7"/>
@@ -22272,7 +22323,7 @@
         <v>555</v>
       </c>
       <c r="B599" s="7" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
       <c r="C599" s="7"/>
       <c r="D599" s="7"/>
@@ -22288,7 +22339,7 @@
         <v>1408</v>
       </c>
       <c r="J599" s="9" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="600" customHeight="1" spans="1:10">
@@ -22296,7 +22347,7 @@
         <v>556</v>
       </c>
       <c r="B600" s="7" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
       <c r="C600" s="7"/>
       <c r="D600" s="7"/>
@@ -22318,7 +22369,7 @@
         <v>557</v>
       </c>
       <c r="B601" s="7" t="s">
-        <v>1665</v>
+        <v>1662</v>
       </c>
       <c r="C601" s="7"/>
       <c r="D601" s="7"/>
@@ -22330,7 +22381,7 @@
         <v>629</v>
       </c>
       <c r="H601" s="9" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
       <c r="I601" s="9" t="s">
         <v>1408</v>
@@ -22342,7 +22393,7 @@
         <v>558</v>
       </c>
       <c r="B602" s="7" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
       <c r="C602" s="7"/>
       <c r="D602" s="7"/>
@@ -22354,13 +22405,13 @@
         <v>1058</v>
       </c>
       <c r="H602" s="9" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
       <c r="I602" s="9" t="s">
         <v>1408</v>
       </c>
       <c r="J602" s="9" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="603" customHeight="1" spans="1:10">
@@ -22368,19 +22419,19 @@
         <v>559</v>
       </c>
       <c r="B603" s="7" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
       <c r="C603" s="7"/>
       <c r="D603" s="7"/>
       <c r="E603" s="9" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="F603" s="7"/>
       <c r="G603" s="7" t="s">
         <v>717</v>
       </c>
       <c r="H603" s="9" t="s">
-        <v>1672</v>
+        <v>1669</v>
       </c>
       <c r="I603" s="9" t="s">
         <v>1408</v>
@@ -22392,12 +22443,12 @@
         <v>560</v>
       </c>
       <c r="B604" s="7" t="s">
-        <v>1673</v>
+        <v>1670</v>
       </c>
       <c r="C604" s="7"/>
       <c r="D604" s="7"/>
       <c r="E604" s="9" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="F604" s="7"/>
       <c r="G604" s="7" t="s">
@@ -22414,19 +22465,19 @@
         <v>561</v>
       </c>
       <c r="B605" s="7" t="s">
-        <v>1674</v>
+        <v>1671</v>
       </c>
       <c r="C605" s="7"/>
       <c r="D605" s="7"/>
       <c r="E605" s="9"/>
       <c r="F605" s="7" t="s">
-        <v>1675</v>
+        <v>1672</v>
       </c>
       <c r="G605" s="7" t="s">
         <v>635</v>
       </c>
       <c r="H605" s="9" t="s">
-        <v>1676</v>
+        <v>1673</v>
       </c>
       <c r="I605" s="9" t="s">
         <v>1408</v>
@@ -22438,15 +22489,15 @@
         <v>562</v>
       </c>
       <c r="B606" s="7" t="s">
-        <v>1677</v>
+        <v>1674</v>
       </c>
       <c r="C606" s="7"/>
       <c r="D606" s="7"/>
       <c r="E606" s="9" t="s">
-        <v>1678</v>
+        <v>1675</v>
       </c>
       <c r="F606" s="7" t="s">
-        <v>1675</v>
+        <v>1672</v>
       </c>
       <c r="G606" s="7" t="s">
         <v>635</v>
@@ -22462,15 +22513,13 @@
         <v>563</v>
       </c>
       <c r="B607" s="7" t="s">
-        <v>1679</v>
+        <v>1676</v>
       </c>
       <c r="C607" s="7"/>
       <c r="D607" s="7"/>
-      <c r="E607" s="18" t="s">
-        <v>1675</v>
-      </c>
+      <c r="E607" s="15"/>
       <c r="F607" s="7" t="s">
-        <v>1675</v>
+        <v>1672</v>
       </c>
       <c r="G607" s="7" t="s">
         <v>635</v>
@@ -22486,15 +22535,13 @@
         <v>564</v>
       </c>
       <c r="B608" s="7" t="s">
-        <v>1680</v>
+        <v>1677</v>
       </c>
       <c r="C608" s="7"/>
       <c r="D608" s="7"/>
-      <c r="E608" s="18" t="s">
-        <v>1675</v>
-      </c>
+      <c r="E608" s="15"/>
       <c r="F608" s="7" t="s">
-        <v>1675</v>
+        <v>1672</v>
       </c>
       <c r="G608" s="7" t="s">
         <v>635</v>
@@ -22510,19 +22557,19 @@
         <v>565</v>
       </c>
       <c r="B609" s="7" t="s">
-        <v>1681</v>
+        <v>1678</v>
       </c>
       <c r="C609" s="7"/>
       <c r="D609" s="7"/>
       <c r="E609" s="9"/>
       <c r="F609" s="7" t="s">
-        <v>1675</v>
+        <v>1672</v>
       </c>
       <c r="G609" s="7" t="s">
         <v>635</v>
       </c>
       <c r="H609" s="9" t="s">
-        <v>1682</v>
+        <v>1679</v>
       </c>
       <c r="I609" s="9" t="s">
         <v>1408</v>
@@ -22534,19 +22581,19 @@
         <v>566</v>
       </c>
       <c r="B610" s="7" t="s">
-        <v>1683</v>
+        <v>1680</v>
       </c>
       <c r="C610" s="7"/>
       <c r="D610" s="7"/>
       <c r="E610" s="9"/>
       <c r="F610" s="7" t="s">
-        <v>1675</v>
+        <v>1672</v>
       </c>
       <c r="G610" s="7" t="s">
         <v>1208</v>
       </c>
       <c r="H610" s="9" t="s">
-        <v>1684</v>
+        <v>1681</v>
       </c>
       <c r="I610" s="9" t="s">
         <v>1408</v>
@@ -22558,15 +22605,13 @@
         <v>567</v>
       </c>
       <c r="B611" s="7" t="s">
-        <v>1685</v>
+        <v>1682</v>
       </c>
       <c r="C611" s="7"/>
       <c r="D611" s="7"/>
-      <c r="E611" s="18" t="s">
-        <v>1675</v>
-      </c>
+      <c r="E611" s="15"/>
       <c r="F611" s="7" t="s">
-        <v>1675</v>
+        <v>1672</v>
       </c>
       <c r="G611" s="7" t="s">
         <v>622</v>
@@ -22582,15 +22627,13 @@
         <v>568</v>
       </c>
       <c r="B612" s="7" t="s">
-        <v>1686</v>
+        <v>1683</v>
       </c>
       <c r="C612" s="7"/>
       <c r="D612" s="7"/>
-      <c r="E612" s="18" t="s">
-        <v>1675</v>
-      </c>
+      <c r="E612" s="15"/>
       <c r="F612" s="7" t="s">
-        <v>1675</v>
+        <v>1672</v>
       </c>
       <c r="G612" s="7" t="s">
         <v>1411</v>
@@ -22606,15 +22649,15 @@
         <v>569</v>
       </c>
       <c r="B613" s="7" t="s">
-        <v>1687</v>
+        <v>1684</v>
       </c>
       <c r="C613" s="7"/>
       <c r="D613" s="7"/>
       <c r="E613" s="9" t="s">
-        <v>1688</v>
+        <v>1685</v>
       </c>
       <c r="F613" s="7" t="s">
-        <v>1675</v>
+        <v>1672</v>
       </c>
       <c r="G613" s="7" t="s">
         <v>1411</v>
@@ -22630,18 +22673,18 @@
         <v>570</v>
       </c>
       <c r="B614" s="7" t="s">
-        <v>1689</v>
+        <v>1686</v>
       </c>
       <c r="C614" s="7"/>
       <c r="D614" s="7"/>
       <c r="E614" s="9" t="s">
-        <v>1678</v>
+        <v>1675</v>
       </c>
       <c r="F614" s="7" t="s">
-        <v>1675</v>
+        <v>1672</v>
       </c>
       <c r="G614" s="7" t="s">
-        <v>1690</v>
+        <v>1687</v>
       </c>
       <c r="H614" s="9"/>
       <c r="I614" s="9" t="s">
@@ -22654,21 +22697,21 @@
         <v>571</v>
       </c>
       <c r="B615" s="7" t="s">
-        <v>1691</v>
+        <v>1688</v>
       </c>
       <c r="C615" s="7"/>
       <c r="D615" s="7"/>
       <c r="E615" s="9" t="s">
-        <v>1692</v>
+        <v>1689</v>
       </c>
       <c r="F615" s="7" t="s">
-        <v>1675</v>
+        <v>1672</v>
       </c>
       <c r="G615" s="7" t="s">
         <v>641</v>
       </c>
       <c r="H615" s="9" t="s">
-        <v>1693</v>
+        <v>1690</v>
       </c>
       <c r="I615" s="9" t="s">
         <v>1408</v>
@@ -22680,15 +22723,13 @@
         <v>572</v>
       </c>
       <c r="B616" s="7" t="s">
-        <v>1694</v>
+        <v>1691</v>
       </c>
       <c r="C616" s="7"/>
       <c r="D616" s="7"/>
-      <c r="E616" s="18" t="s">
-        <v>1675</v>
-      </c>
+      <c r="E616" s="15"/>
       <c r="F616" s="7" t="s">
-        <v>1675</v>
+        <v>1672</v>
       </c>
       <c r="G616" s="7" t="s">
         <v>618</v>
@@ -22704,15 +22745,15 @@
         <v>573</v>
       </c>
       <c r="B617" s="7" t="s">
-        <v>1695</v>
+        <v>1692</v>
       </c>
       <c r="C617" s="7"/>
       <c r="D617" s="7"/>
       <c r="E617" s="9" t="s">
-        <v>1678</v>
+        <v>1675</v>
       </c>
       <c r="F617" s="7" t="s">
-        <v>1675</v>
+        <v>1672</v>
       </c>
       <c r="G617" s="7" t="s">
         <v>618</v>
@@ -22728,21 +22769,21 @@
         <v>574</v>
       </c>
       <c r="B618" s="7" t="s">
-        <v>1696</v>
+        <v>1693</v>
       </c>
       <c r="C618" s="7"/>
       <c r="D618" s="7"/>
       <c r="E618" s="9" t="s">
-        <v>1697</v>
+        <v>1694</v>
       </c>
       <c r="F618" s="7" t="s">
-        <v>1675</v>
+        <v>1672</v>
       </c>
       <c r="G618" s="7" t="s">
         <v>618</v>
       </c>
       <c r="H618" s="9" t="s">
-        <v>1698</v>
+        <v>1695</v>
       </c>
       <c r="I618" s="9" t="s">
         <v>1408</v>
@@ -22754,15 +22795,15 @@
         <v>575</v>
       </c>
       <c r="B619" s="7" t="s">
-        <v>1699</v>
+        <v>1696</v>
       </c>
       <c r="C619" s="7"/>
       <c r="D619" s="7"/>
       <c r="E619" s="9" t="s">
-        <v>1678</v>
+        <v>1675</v>
       </c>
       <c r="F619" s="7" t="s">
-        <v>1675</v>
+        <v>1672</v>
       </c>
       <c r="G619" s="7" t="s">
         <v>638</v>
@@ -22778,21 +22819,21 @@
         <v>576</v>
       </c>
       <c r="B620" s="7" t="s">
-        <v>1700</v>
+        <v>1697</v>
       </c>
       <c r="C620" s="7"/>
       <c r="D620" s="7"/>
       <c r="E620" s="9" t="s">
-        <v>1701</v>
+        <v>1698</v>
       </c>
       <c r="F620" s="7" t="s">
-        <v>1675</v>
+        <v>1672</v>
       </c>
       <c r="G620" s="7" t="s">
         <v>638</v>
       </c>
       <c r="H620" s="9" t="s">
-        <v>1702</v>
+        <v>1699</v>
       </c>
       <c r="I620" s="9" t="s">
         <v>1408</v>
@@ -22804,12 +22845,12 @@
         <v>577</v>
       </c>
       <c r="B621" s="7" t="s">
-        <v>1703</v>
+        <v>1700</v>
       </c>
       <c r="C621" s="7"/>
       <c r="D621" s="7"/>
       <c r="E621" s="9" t="s">
-        <v>1704</v>
+        <v>1701</v>
       </c>
       <c r="F621" s="7" t="s">
         <v>894</v>
@@ -22828,13 +22869,11 @@
         <v>578</v>
       </c>
       <c r="B622" s="7" t="s">
-        <v>1705</v>
+        <v>1702</v>
       </c>
       <c r="C622" s="7"/>
       <c r="D622" s="7"/>
-      <c r="E622" s="9" t="s">
-        <v>1706</v>
-      </c>
+      <c r="E622" s="9"/>
       <c r="F622" s="7" t="s">
         <v>894</v>
       </c>
@@ -22842,10 +22881,10 @@
         <v>717</v>
       </c>
       <c r="H622" s="9" t="s">
-        <v>1707</v>
+        <v>1703</v>
       </c>
       <c r="I622" s="9" t="s">
-        <v>1508</v>
+        <v>1505</v>
       </c>
       <c r="J622" s="9"/>
     </row>
@@ -22854,7 +22893,7 @@
         <v>579</v>
       </c>
       <c r="B623" s="7" t="s">
-        <v>1708</v>
+        <v>1704</v>
       </c>
       <c r="C623" s="7"/>
       <c r="D623" s="7"/>
@@ -22866,10 +22905,10 @@
         <v>641</v>
       </c>
       <c r="H623" s="9" t="s">
-        <v>1709</v>
+        <v>1705</v>
       </c>
       <c r="I623" s="9" t="s">
-        <v>1498</v>
+        <v>1495</v>
       </c>
       <c r="J623" s="9"/>
     </row>
@@ -22878,7 +22917,7 @@
         <v>580</v>
       </c>
       <c r="B624" s="7" t="s">
-        <v>1710</v>
+        <v>1706</v>
       </c>
       <c r="C624" s="7"/>
       <c r="D624" s="7"/>
@@ -22890,7 +22929,7 @@
         <v>618</v>
       </c>
       <c r="H624" s="9" t="s">
-        <v>1711</v>
+        <v>1707</v>
       </c>
       <c r="I624" s="9" t="s">
         <v>1408</v>
@@ -22902,13 +22941,13 @@
         <v>581</v>
       </c>
       <c r="B625" s="7" t="s">
-        <v>1712</v>
+        <v>1708</v>
       </c>
       <c r="C625" s="7"/>
       <c r="D625" s="7"/>
       <c r="E625" s="9"/>
       <c r="F625" s="7" t="s">
-        <v>1713</v>
+        <v>1709</v>
       </c>
       <c r="G625" s="7" t="s">
         <v>635</v>
@@ -22924,15 +22963,15 @@
         <v>582</v>
       </c>
       <c r="B626" s="7" t="s">
-        <v>1714</v>
+        <v>1710</v>
       </c>
       <c r="C626" s="7"/>
       <c r="D626" s="7"/>
       <c r="E626" s="9" t="s">
-        <v>1715</v>
+        <v>1711</v>
       </c>
       <c r="F626" s="7" t="s">
-        <v>1713</v>
+        <v>1709</v>
       </c>
       <c r="G626" s="7" t="s">
         <v>641</v>
@@ -22948,19 +22987,19 @@
         <v>583</v>
       </c>
       <c r="B627" s="7" t="s">
-        <v>1716</v>
+        <v>1712</v>
       </c>
       <c r="C627" s="7"/>
       <c r="D627" s="7"/>
       <c r="E627" s="9"/>
       <c r="F627" s="7" t="s">
-        <v>1713</v>
+        <v>1709</v>
       </c>
       <c r="G627" s="7" t="s">
         <v>618</v>
       </c>
       <c r="H627" s="9" t="s">
-        <v>1717</v>
+        <v>1713</v>
       </c>
       <c r="I627" s="9" t="s">
         <v>1408</v>
@@ -22972,13 +23011,13 @@
         <v>584</v>
       </c>
       <c r="B628" s="7" t="s">
-        <v>1718</v>
+        <v>1714</v>
       </c>
       <c r="C628" s="7"/>
       <c r="D628" s="7"/>
       <c r="E628" s="9"/>
       <c r="F628" s="7" t="s">
-        <v>1713</v>
+        <v>1709</v>
       </c>
       <c r="G628" s="7" t="s">
         <v>638</v>
@@ -22994,13 +23033,13 @@
         <v>585</v>
       </c>
       <c r="B629" s="7" t="s">
-        <v>1719</v>
+        <v>1715</v>
       </c>
       <c r="C629" s="7"/>
       <c r="D629" s="7"/>
       <c r="E629" s="9"/>
       <c r="F629" s="7" t="s">
-        <v>1713</v>
+        <v>1709</v>
       </c>
       <c r="G629" s="7" t="s">
         <v>629</v>
@@ -23016,12 +23055,12 @@
         <v>586</v>
       </c>
       <c r="B630" s="7" t="s">
-        <v>1720</v>
+        <v>1716</v>
       </c>
       <c r="C630" s="7"/>
       <c r="D630" s="7"/>
       <c r="E630" s="9" t="s">
-        <v>1721</v>
+        <v>1717</v>
       </c>
       <c r="F630" s="7"/>
       <c r="G630" s="7" t="s">
@@ -23038,7 +23077,7 @@
         <v>587</v>
       </c>
       <c r="B631" s="7" t="s">
-        <v>1722</v>
+        <v>1718</v>
       </c>
       <c r="C631" s="7"/>
       <c r="D631" s="7"/>
@@ -23051,7 +23090,7 @@
       </c>
       <c r="H631" s="9"/>
       <c r="I631" s="9" t="s">
-        <v>1508</v>
+        <v>1505</v>
       </c>
       <c r="J631" s="9"/>
     </row>
@@ -23060,12 +23099,12 @@
         <v>588</v>
       </c>
       <c r="B632" s="7" t="s">
-        <v>1723</v>
+        <v>1719</v>
       </c>
       <c r="C632" s="7"/>
       <c r="D632" s="7"/>
       <c r="E632" s="9" t="s">
-        <v>1724</v>
+        <v>1720</v>
       </c>
       <c r="F632" s="7"/>
       <c r="G632" s="7" t="s">
@@ -23073,7 +23112,7 @@
       </c>
       <c r="H632" s="9"/>
       <c r="I632" s="9" t="s">
-        <v>1508</v>
+        <v>1505</v>
       </c>
       <c r="J632" s="9"/>
     </row>
@@ -23082,7 +23121,7 @@
         <v>589</v>
       </c>
       <c r="B633" s="7" t="s">
-        <v>1725</v>
+        <v>1721</v>
       </c>
       <c r="C633" s="7"/>
       <c r="D633" s="7"/>
@@ -23095,7 +23134,7 @@
       </c>
       <c r="H633" s="9"/>
       <c r="I633" s="9" t="s">
-        <v>1508</v>
+        <v>1505</v>
       </c>
       <c r="J633" s="9"/>
     </row>
@@ -23104,7 +23143,7 @@
         <v>590</v>
       </c>
       <c r="B634" s="7" t="s">
-        <v>1726</v>
+        <v>1722</v>
       </c>
       <c r="C634" s="7"/>
       <c r="D634" s="7"/>
@@ -23116,13 +23155,13 @@
         <v>717</v>
       </c>
       <c r="H634" s="9" t="s">
-        <v>1727</v>
+        <v>1723</v>
       </c>
       <c r="I634" s="9" t="s">
-        <v>1508</v>
+        <v>1505</v>
       </c>
       <c r="J634" s="9" t="s">
-        <v>1728</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="635" customHeight="1" spans="1:10">
@@ -23130,7 +23169,7 @@
         <v>591</v>
       </c>
       <c r="B635" s="7" t="s">
-        <v>1729</v>
+        <v>1725</v>
       </c>
       <c r="C635" s="7"/>
       <c r="D635" s="7"/>
@@ -23142,10 +23181,10 @@
         <v>622</v>
       </c>
       <c r="H635" s="9" t="s">
-        <v>1730</v>
+        <v>1726</v>
       </c>
       <c r="I635" s="9" t="s">
-        <v>1508</v>
+        <v>1505</v>
       </c>
       <c r="J635" s="9"/>
     </row>
@@ -23154,7 +23193,7 @@
         <v>592</v>
       </c>
       <c r="B636" s="7" t="s">
-        <v>1731</v>
+        <v>1727</v>
       </c>
       <c r="C636" s="7"/>
       <c r="D636" s="7"/>
@@ -23166,13 +23205,13 @@
         <v>717</v>
       </c>
       <c r="H636" s="9" t="s">
-        <v>1732</v>
+        <v>1728</v>
       </c>
       <c r="I636" s="9" t="s">
-        <v>1508</v>
+        <v>1505</v>
       </c>
       <c r="J636" s="9" t="s">
-        <v>1733</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="637" customHeight="1" spans="1:10">
@@ -23180,7 +23219,7 @@
         <v>593</v>
       </c>
       <c r="B637" s="7" t="s">
-        <v>1734</v>
+        <v>1730</v>
       </c>
       <c r="C637" s="7"/>
       <c r="D637" s="7"/>
@@ -23192,13 +23231,13 @@
         <v>717</v>
       </c>
       <c r="H637" s="9" t="s">
-        <v>1735</v>
+        <v>1731</v>
       </c>
       <c r="I637" s="9" t="s">
-        <v>1508</v>
+        <v>1505</v>
       </c>
       <c r="J637" s="9" t="s">
-        <v>1736</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="638" customHeight="1" spans="1:10">
@@ -23206,7 +23245,7 @@
         <v>594</v>
       </c>
       <c r="B638" s="7" t="s">
-        <v>1737</v>
+        <v>1733</v>
       </c>
       <c r="C638" s="7"/>
       <c r="D638" s="7"/>
@@ -23218,10 +23257,10 @@
         <v>641</v>
       </c>
       <c r="H638" s="9" t="s">
-        <v>1738</v>
+        <v>1734</v>
       </c>
       <c r="I638" s="9" t="s">
-        <v>1508</v>
+        <v>1505</v>
       </c>
       <c r="J638" s="9"/>
     </row>
@@ -23230,7 +23269,7 @@
         <v>595</v>
       </c>
       <c r="B639" s="7" t="s">
-        <v>1739</v>
+        <v>1735</v>
       </c>
       <c r="C639" s="7"/>
       <c r="D639" s="7"/>
@@ -23242,13 +23281,13 @@
         <v>717</v>
       </c>
       <c r="H639" s="9" t="s">
-        <v>1740</v>
+        <v>1736</v>
       </c>
       <c r="I639" s="9" t="s">
-        <v>1508</v>
+        <v>1505</v>
       </c>
       <c r="J639" s="9" t="s">
-        <v>1733</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="640" customHeight="1" spans="1:10">
@@ -23256,7 +23295,7 @@
         <v>596</v>
       </c>
       <c r="B640" s="7" t="s">
-        <v>1741</v>
+        <v>1737</v>
       </c>
       <c r="C640" s="7"/>
       <c r="D640" s="7"/>
@@ -23268,13 +23307,13 @@
         <v>717</v>
       </c>
       <c r="H640" s="9" t="s">
-        <v>1742</v>
+        <v>1738</v>
       </c>
       <c r="I640" s="9" t="s">
-        <v>1508</v>
+        <v>1505</v>
       </c>
       <c r="J640" s="9" t="s">
-        <v>1728</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="641" customHeight="1" spans="1:10">
@@ -23282,7 +23321,7 @@
         <v>597</v>
       </c>
       <c r="B641" s="7" t="s">
-        <v>1743</v>
+        <v>1739</v>
       </c>
       <c r="C641" s="7"/>
       <c r="D641" s="7"/>
@@ -23294,13 +23333,13 @@
         <v>717</v>
       </c>
       <c r="H641" s="9" t="s">
-        <v>1744</v>
+        <v>1740</v>
       </c>
       <c r="I641" s="9" t="s">
-        <v>1508</v>
+        <v>1505</v>
       </c>
       <c r="J641" s="9" t="s">
-        <v>1736</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="642" customHeight="1" spans="1:10">
@@ -23308,7 +23347,7 @@
         <v>598</v>
       </c>
       <c r="B642" s="7" t="s">
-        <v>1745</v>
+        <v>1741</v>
       </c>
       <c r="C642" s="7"/>
       <c r="D642" s="7"/>
@@ -23321,7 +23360,7 @@
       </c>
       <c r="H642" s="9"/>
       <c r="I642" s="9" t="s">
-        <v>1508</v>
+        <v>1505</v>
       </c>
       <c r="J642" s="9"/>
     </row>
@@ -23330,7 +23369,7 @@
         <v>599</v>
       </c>
       <c r="B643" s="7" t="s">
-        <v>1746</v>
+        <v>1742</v>
       </c>
       <c r="C643" s="7"/>
       <c r="D643" s="7"/>
@@ -23343,7 +23382,7 @@
       </c>
       <c r="H643" s="9"/>
       <c r="I643" s="9" t="s">
-        <v>1508</v>
+        <v>1505</v>
       </c>
       <c r="J643" s="9"/>
     </row>
@@ -23352,22 +23391,22 @@
         <v>600</v>
       </c>
       <c r="B644" s="7" t="s">
-        <v>1747</v>
+        <v>1743</v>
       </c>
       <c r="C644" s="7"/>
       <c r="D644" s="7"/>
       <c r="E644" s="9" t="s">
-        <v>1748</v>
+        <v>1744</v>
       </c>
       <c r="F644" s="7"/>
       <c r="G644" s="7" t="s">
         <v>638</v>
       </c>
       <c r="H644" s="9" t="s">
-        <v>1749</v>
+        <v>1745</v>
       </c>
       <c r="I644" s="9" t="s">
-        <v>1508</v>
+        <v>1505</v>
       </c>
       <c r="J644" s="9"/>
     </row>
@@ -23376,7 +23415,7 @@
         <v>601</v>
       </c>
       <c r="B645" s="7" t="s">
-        <v>1750</v>
+        <v>1746</v>
       </c>
       <c r="C645" s="7"/>
       <c r="D645" s="7"/>
@@ -23389,7 +23428,7 @@
       </c>
       <c r="H645" s="9"/>
       <c r="I645" s="9" t="s">
-        <v>1508</v>
+        <v>1505</v>
       </c>
       <c r="J645" s="9"/>
     </row>
@@ -23398,7 +23437,7 @@
         <v>602</v>
       </c>
       <c r="B646" s="7" t="s">
-        <v>1751</v>
+        <v>1747</v>
       </c>
       <c r="C646" s="7"/>
       <c r="D646" s="7"/>
@@ -23411,7 +23450,7 @@
       </c>
       <c r="H646" s="9"/>
       <c r="I646" s="9" t="s">
-        <v>1508</v>
+        <v>1505</v>
       </c>
       <c r="J646" s="9"/>
     </row>
@@ -23420,7 +23459,7 @@
         <v>603</v>
       </c>
       <c r="B647" s="7" t="s">
-        <v>1752</v>
+        <v>1748</v>
       </c>
       <c r="C647" s="7"/>
       <c r="D647" s="7"/>
@@ -23432,10 +23471,10 @@
         <v>626</v>
       </c>
       <c r="H647" s="9" t="s">
-        <v>1753</v>
+        <v>1749</v>
       </c>
       <c r="I647" s="9" t="s">
-        <v>1508</v>
+        <v>1505</v>
       </c>
       <c r="J647" s="9"/>
     </row>
@@ -23444,7 +23483,7 @@
         <v>604</v>
       </c>
       <c r="B648" s="7" t="s">
-        <v>1754</v>
+        <v>1750</v>
       </c>
       <c r="C648" s="7"/>
       <c r="D648" s="7"/>
@@ -23457,7 +23496,7 @@
       </c>
       <c r="H648" s="9"/>
       <c r="I648" s="9" t="s">
-        <v>1508</v>
+        <v>1505</v>
       </c>
       <c r="J648" s="9"/>
     </row>
@@ -23466,22 +23505,22 @@
         <v>605</v>
       </c>
       <c r="B649" s="7" t="s">
-        <v>1755</v>
+        <v>1751</v>
       </c>
       <c r="C649" s="7"/>
       <c r="D649" s="7"/>
       <c r="E649" s="9" t="s">
-        <v>1756</v>
+        <v>1752</v>
       </c>
       <c r="F649" s="7"/>
       <c r="G649" s="7" t="s">
         <v>618</v>
       </c>
       <c r="H649" s="9" t="s">
-        <v>1757</v>
+        <v>1753</v>
       </c>
       <c r="I649" s="9" t="s">
-        <v>1758</v>
+        <v>1754</v>
       </c>
       <c r="J649" s="9"/>
     </row>
@@ -23490,12 +23529,12 @@
         <v>606</v>
       </c>
       <c r="B650" s="7" t="s">
-        <v>1759</v>
+        <v>1755</v>
       </c>
       <c r="C650" s="7"/>
       <c r="D650" s="7"/>
       <c r="E650" s="9" t="s">
-        <v>1756</v>
+        <v>1752</v>
       </c>
       <c r="F650" s="7"/>
       <c r="G650" s="7" t="s">
@@ -23505,7 +23544,7 @@
         <v>1381</v>
       </c>
       <c r="I650" s="9" t="s">
-        <v>1758</v>
+        <v>1754</v>
       </c>
       <c r="J650" s="9"/>
     </row>
@@ -23514,22 +23553,22 @@
         <v>607</v>
       </c>
       <c r="B651" s="7" t="s">
-        <v>1760</v>
+        <v>1756</v>
       </c>
       <c r="C651" s="7"/>
       <c r="D651" s="7"/>
       <c r="E651" s="9" t="s">
-        <v>1756</v>
+        <v>1752</v>
       </c>
       <c r="F651" s="7"/>
       <c r="G651" s="7" t="s">
         <v>629</v>
       </c>
       <c r="H651" s="9" t="s">
-        <v>1761</v>
+        <v>1757</v>
       </c>
       <c r="I651" s="9" t="s">
-        <v>1758</v>
+        <v>1754</v>
       </c>
       <c r="J651" s="9"/>
     </row>
@@ -23538,12 +23577,12 @@
         <v>608</v>
       </c>
       <c r="B652" s="7" t="s">
-        <v>1762</v>
+        <v>1758</v>
       </c>
       <c r="C652" s="7"/>
       <c r="D652" s="7"/>
       <c r="E652" s="9" t="s">
-        <v>1756</v>
+        <v>1752</v>
       </c>
       <c r="F652" s="7"/>
       <c r="G652" s="7" t="s">
@@ -23551,7 +23590,7 @@
       </c>
       <c r="H652" s="9"/>
       <c r="I652" s="9" t="s">
-        <v>1758</v>
+        <v>1754</v>
       </c>
       <c r="J652" s="9"/>
     </row>
@@ -23560,22 +23599,22 @@
         <v>609</v>
       </c>
       <c r="B653" s="7" t="s">
-        <v>1763</v>
+        <v>1759</v>
       </c>
       <c r="C653" s="7"/>
       <c r="D653" s="7"/>
       <c r="E653" s="9" t="s">
-        <v>1756</v>
+        <v>1752</v>
       </c>
       <c r="F653" s="7"/>
       <c r="G653" s="7" t="s">
         <v>638</v>
       </c>
       <c r="H653" s="9" t="s">
-        <v>1764</v>
+        <v>1760</v>
       </c>
       <c r="I653" s="9" t="s">
-        <v>1758</v>
+        <v>1754</v>
       </c>
       <c r="J653" s="9"/>
     </row>
@@ -23584,22 +23623,22 @@
         <v>610</v>
       </c>
       <c r="B654" s="7" t="s">
-        <v>1765</v>
+        <v>1761</v>
       </c>
       <c r="C654" s="7"/>
       <c r="D654" s="7"/>
       <c r="E654" s="9" t="s">
-        <v>1756</v>
+        <v>1752</v>
       </c>
       <c r="F654" s="7"/>
       <c r="G654" s="7" t="s">
         <v>668</v>
       </c>
       <c r="H654" s="9" t="s">
-        <v>1766</v>
+        <v>1762</v>
       </c>
       <c r="I654" s="9" t="s">
-        <v>1758</v>
+        <v>1754</v>
       </c>
       <c r="J654" s="9"/>
     </row>
@@ -23608,12 +23647,12 @@
         <v>611</v>
       </c>
       <c r="B655" s="7" t="s">
-        <v>1767</v>
+        <v>1763</v>
       </c>
       <c r="C655" s="7"/>
       <c r="D655" s="7"/>
       <c r="E655" s="9" t="s">
-        <v>1756</v>
+        <v>1752</v>
       </c>
       <c r="F655" s="7"/>
       <c r="G655" s="7" t="s">
@@ -23621,7 +23660,7 @@
       </c>
       <c r="H655" s="9"/>
       <c r="I655" s="9" t="s">
-        <v>1758</v>
+        <v>1754</v>
       </c>
       <c r="J655" s="9"/>
     </row>
@@ -23630,12 +23669,12 @@
         <v>612</v>
       </c>
       <c r="B656" s="7" t="s">
-        <v>1768</v>
+        <v>1764</v>
       </c>
       <c r="C656" s="7"/>
       <c r="D656" s="7"/>
       <c r="E656" s="9" t="s">
-        <v>1756</v>
+        <v>1752</v>
       </c>
       <c r="F656" s="7"/>
       <c r="G656" s="7" t="s">
@@ -23643,13 +23682,263 @@
       </c>
       <c r="H656" s="9"/>
       <c r="I656" s="9" t="s">
-        <v>1758</v>
+        <v>1754</v>
       </c>
       <c r="J656" s="9"/>
     </row>
+    <row r="657" customHeight="1" spans="1:10">
+      <c r="A657" s="6">
+        <v>999.01</v>
+      </c>
+      <c r="B657" s="7" t="s">
+        <v>1765</v>
+      </c>
+      <c r="C657" s="7"/>
+      <c r="D657" s="7"/>
+      <c r="E657" s="9" t="s">
+        <v>1766</v>
+      </c>
+      <c r="F657" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G657" s="7"/>
+      <c r="H657" s="9"/>
+      <c r="I657" s="9"/>
+      <c r="J657" s="9"/>
+    </row>
+    <row r="658" customHeight="1" spans="1:10">
+      <c r="A658" s="6">
+        <v>999.02</v>
+      </c>
+      <c r="B658" s="7" t="s">
+        <v>1767</v>
+      </c>
+      <c r="C658" s="7"/>
+      <c r="D658" s="7"/>
+      <c r="E658" s="9"/>
+      <c r="F658" s="7"/>
+      <c r="G658" s="7"/>
+      <c r="H658" s="9"/>
+      <c r="I658" s="9"/>
+      <c r="J658" s="9"/>
+    </row>
+    <row r="659" customHeight="1" spans="1:10">
+      <c r="A659" s="6">
+        <v>999.03</v>
+      </c>
+      <c r="B659" s="7" t="s">
+        <v>1768</v>
+      </c>
+      <c r="C659" s="7"/>
+      <c r="D659" s="7"/>
+      <c r="E659" s="9" t="s">
+        <v>1769</v>
+      </c>
+      <c r="F659" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G659" s="7"/>
+      <c r="H659" s="9"/>
+      <c r="I659" s="9"/>
+      <c r="J659" s="9"/>
+    </row>
+    <row r="660" customHeight="1" spans="1:10">
+      <c r="A660" s="6">
+        <v>999.04</v>
+      </c>
+      <c r="B660" s="7" t="s">
+        <v>1770</v>
+      </c>
+      <c r="C660" s="7"/>
+      <c r="D660" s="7"/>
+      <c r="E660" s="9" t="s">
+        <v>1771</v>
+      </c>
+      <c r="F660" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G660" s="7"/>
+      <c r="H660" s="9"/>
+      <c r="I660" s="9"/>
+      <c r="J660" s="9"/>
+    </row>
+    <row r="661" customHeight="1" spans="1:10">
+      <c r="A661" s="6">
+        <v>999.05</v>
+      </c>
+      <c r="B661" s="7" t="s">
+        <v>1772</v>
+      </c>
+      <c r="C661" s="7"/>
+      <c r="D661" s="7"/>
+      <c r="E661" s="9"/>
+      <c r="F661" s="7"/>
+      <c r="G661" s="7"/>
+      <c r="H661" s="9"/>
+      <c r="I661" s="9"/>
+      <c r="J661" s="9"/>
+    </row>
+    <row r="662" customHeight="1" spans="1:10">
+      <c r="A662" s="6">
+        <v>999.06</v>
+      </c>
+      <c r="B662" s="7" t="s">
+        <v>1773</v>
+      </c>
+      <c r="C662" s="7"/>
+      <c r="D662" s="7"/>
+      <c r="E662" s="9" t="s">
+        <v>1774</v>
+      </c>
+      <c r="F662" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G662" s="7"/>
+      <c r="H662" s="9"/>
+      <c r="I662" s="9"/>
+      <c r="J662" s="9"/>
+    </row>
+    <row r="663" customHeight="1" spans="1:10">
+      <c r="A663" s="6">
+        <v>999.07</v>
+      </c>
+      <c r="B663" s="7" t="s">
+        <v>1775</v>
+      </c>
+      <c r="C663" s="7"/>
+      <c r="D663" s="7"/>
+      <c r="E663" s="9" t="s">
+        <v>1776</v>
+      </c>
+      <c r="F663" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G663" s="7"/>
+      <c r="H663" s="9"/>
+      <c r="I663" s="9"/>
+      <c r="J663" s="9"/>
+    </row>
+    <row r="664" customHeight="1" spans="1:10">
+      <c r="A664" s="6">
+        <v>999.08</v>
+      </c>
+      <c r="B664" s="7" t="s">
+        <v>1777</v>
+      </c>
+      <c r="C664" s="7"/>
+      <c r="D664" s="7"/>
+      <c r="E664" s="9" t="s">
+        <v>1778</v>
+      </c>
+      <c r="F664" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G664" s="7"/>
+      <c r="H664" s="9"/>
+      <c r="I664" s="9"/>
+      <c r="J664" s="9"/>
+    </row>
+    <row r="665" customHeight="1" spans="1:10">
+      <c r="A665" s="6">
+        <v>999.09</v>
+      </c>
+      <c r="B665" s="7" t="s">
+        <v>1779</v>
+      </c>
+      <c r="C665" s="7"/>
+      <c r="D665" s="7"/>
+      <c r="E665" s="9" t="s">
+        <v>1780</v>
+      </c>
+      <c r="F665" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G665" s="7"/>
+      <c r="H665" s="9"/>
+      <c r="I665" s="9"/>
+      <c r="J665" s="9"/>
+    </row>
+    <row r="666" customHeight="1" spans="1:10">
+      <c r="A666" s="6">
+        <v>999.1</v>
+      </c>
+      <c r="B666" s="7" t="s">
+        <v>1781</v>
+      </c>
+      <c r="C666" s="7"/>
+      <c r="D666" s="7"/>
+      <c r="E666" s="9" t="s">
+        <v>1782</v>
+      </c>
+      <c r="F666" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G666" s="7"/>
+      <c r="H666" s="9"/>
+      <c r="I666" s="9"/>
+      <c r="J666" s="9"/>
+    </row>
+    <row r="667" customHeight="1" spans="1:10">
+      <c r="A667" s="6">
+        <v>999.11</v>
+      </c>
+      <c r="B667" s="7" t="s">
+        <v>1783</v>
+      </c>
+      <c r="C667" s="7"/>
+      <c r="D667" s="7"/>
+      <c r="E667" s="9" t="s">
+        <v>1784</v>
+      </c>
+      <c r="F667" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G667" s="7"/>
+      <c r="H667" s="9"/>
+      <c r="I667" s="9"/>
+      <c r="J667" s="9"/>
+    </row>
+    <row r="668" customHeight="1" spans="1:10">
+      <c r="A668" s="6">
+        <v>999.12</v>
+      </c>
+      <c r="B668" s="7" t="s">
+        <v>1785</v>
+      </c>
+      <c r="C668" s="7"/>
+      <c r="D668" s="7"/>
+      <c r="E668" s="9"/>
+      <c r="F668" s="7"/>
+      <c r="G668" s="7"/>
+      <c r="H668" s="9"/>
+      <c r="I668" s="9"/>
+      <c r="J668" s="9"/>
+    </row>
+    <row r="669" customHeight="1" spans="1:10">
+      <c r="A669" s="6">
+        <v>999.15</v>
+      </c>
+      <c r="B669" s="7" t="s">
+        <v>1786</v>
+      </c>
+      <c r="C669" s="7"/>
+      <c r="D669" s="7"/>
+      <c r="E669" s="9" t="s">
+        <v>1787</v>
+      </c>
+      <c r="F669" s="7" t="s">
+        <v>1376</v>
+      </c>
+      <c r="G669" s="7"/>
+      <c r="H669" s="9"/>
+      <c r="I669" s="9"/>
+      <c r="J669" s="9" t="s">
+        <v>1788</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:J656" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A1:J656">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:J669" etc:filterBottomFollowUsedRange="0">
+    <sortState ref="A2:J669">
       <sortCondition ref="A1"/>
     </sortState>
     <extLst/>
@@ -23657,7 +23946,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="D1:F1 H1 J1" formula="1"/>
+    <ignoredError sqref="J1 H1 D1:F1" formula="1"/>
   </ignoredErrors>
 </worksheet>
 </file>